--- a/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/data/mapping_config_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C137B89-7225-614A-A598-98BF8E16F133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146ED0C6-1909-C347-8450-9D721F37F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20860" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
@@ -3088,7 +3088,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -14529,7 +14529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}">
   <dimension ref="A1:K112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
@@ -14543,7 +14543,7 @@
     <col min="11" max="11" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="37" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="37" customFormat="1" ht="19">
       <c r="A1" s="37" t="s">
         <v>666</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" s="25" customFormat="1">
       <c r="A2" s="25" t="b">
         <v>1</v>
       </c>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="H2" s="42"/>
     </row>
-    <row r="3" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" s="25" customFormat="1">
       <c r="A3" s="25" t="b">
         <v>1</v>
       </c>
@@ -14617,7 +14617,7 @@
       </c>
       <c r="H3" s="42"/>
     </row>
-    <row r="4" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" s="25" customFormat="1">
       <c r="A4" s="25" t="b">
         <v>0</v>
       </c>
@@ -14638,10 +14638,10 @@
         <v>875</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" s="25" customFormat="1">
       <c r="H5" s="42"/>
     </row>
-    <row r="6" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" s="25" customFormat="1">
       <c r="A6" s="25" t="b">
         <v>1</v>
       </c>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="H6" s="42"/>
     </row>
-    <row r="7" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" s="25" customFormat="1">
       <c r="A7" s="25" t="b">
         <v>1</v>
       </c>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="H7" s="42"/>
     </row>
-    <row r="8" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" s="25" customFormat="1">
       <c r="A8" s="25" t="b">
         <v>1</v>
       </c>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H8" s="42"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" s="25" customFormat="1">
       <c r="A9" s="25" t="b">
         <v>0</v>
       </c>
@@ -14720,7 +14720,7 @@
       </c>
       <c r="H9" s="42"/>
     </row>
-    <row r="10" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" s="25" customFormat="1">
       <c r="A10" s="25" t="b">
         <v>0</v>
       </c>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="H10" s="42"/>
     </row>
-    <row r="11" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" s="25" customFormat="1">
       <c r="A11" s="25" t="b">
         <v>0</v>
       </c>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="H11" s="42"/>
     </row>
-    <row r="12" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" s="25" customFormat="1">
       <c r="A12" s="25" t="b">
         <v>0</v>
       </c>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="H12" s="42"/>
     </row>
-    <row r="13" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" s="25" customFormat="1">
       <c r="A13" s="25" t="b">
         <v>0</v>
       </c>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="H13" s="42"/>
     </row>
-    <row r="14" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" s="25" customFormat="1">
       <c r="A14" s="25" t="b">
         <v>0</v>
       </c>
@@ -14795,7 +14795,7 @@
       </c>
       <c r="H14" s="42"/>
     </row>
-    <row r="15" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" s="25" customFormat="1">
       <c r="A15" s="25" t="b">
         <v>0</v>
       </c>
@@ -14810,10 +14810,10 @@
       </c>
       <c r="H15" s="42"/>
     </row>
-    <row r="16" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" s="25" customFormat="1">
       <c r="H16" s="42"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" s="25" t="b">
         <v>1</v>
       </c>
@@ -14834,7 +14834,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="25"/>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
@@ -14843,7 +14843,7 @@
       <c r="F18" s="25"/>
       <c r="G18" s="25"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" s="25" t="b">
         <v>1</v>
       </c>
@@ -14864,7 +14864,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" s="25" customFormat="1">
       <c r="A20" s="25" t="b">
         <v>1</v>
       </c>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="H20" s="42"/>
     </row>
-    <row r="21" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" s="25" customFormat="1">
       <c r="A21" s="25" t="b">
         <v>0</v>
       </c>
@@ -14906,7 +14906,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" s="25" customFormat="1">
       <c r="A22" s="25" t="b">
         <v>1</v>
       </c>
@@ -14927,10 +14927,10 @@
       </c>
       <c r="H22" s="42"/>
     </row>
-    <row r="23" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" s="25" customFormat="1">
       <c r="H23" s="42"/>
     </row>
-    <row r="24" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" s="25" customFormat="1">
       <c r="A24" s="25" t="b">
         <v>1</v>
       </c>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="H24" s="42"/>
     </row>
-    <row r="25" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" s="25" customFormat="1">
       <c r="A25" s="25" t="b">
         <v>0</v>
       </c>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="H25" s="42"/>
     </row>
-    <row r="26" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" s="25" customFormat="1">
       <c r="A26" s="25" t="b">
         <v>1</v>
       </c>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="H26" s="42"/>
     </row>
-    <row r="27" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" s="25" customFormat="1">
       <c r="A27" s="25" t="b">
         <v>1</v>
       </c>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="H27" s="42"/>
     </row>
-    <row r="28" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" s="25" customFormat="1">
       <c r="A28" s="25" t="b">
         <v>1</v>
       </c>
@@ -15037,7 +15037,7 @@
       <c r="H28" s="42"/>
       <c r="K28" s="17"/>
     </row>
-    <row r="29" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" s="25" customFormat="1">
       <c r="A29" s="25" t="b">
         <v>1</v>
       </c>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="H29" s="42"/>
     </row>
-    <row r="30" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" s="25" customFormat="1">
       <c r="A30" s="25" t="b">
         <v>1</v>
       </c>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="H30" s="42"/>
     </row>
-    <row r="31" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" s="25" customFormat="1">
       <c r="A31" s="25" t="b">
         <v>1</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" s="25" customFormat="1">
       <c r="A32" s="25" t="b">
         <v>0</v>
       </c>
@@ -15117,10 +15117,10 @@
         <v>985</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" s="25" customFormat="1">
       <c r="H33" s="44"/>
     </row>
-    <row r="34" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" s="25" customFormat="1">
       <c r="A34" s="25" t="b">
         <v>0</v>
       </c>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="H34" s="44"/>
     </row>
-    <row r="35" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" s="25" customFormat="1">
       <c r="A35" s="25" t="b">
         <v>1</v>
       </c>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="H35" s="44"/>
     </row>
-    <row r="36" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" s="25" customFormat="1">
       <c r="A36" s="25" t="b">
         <v>1</v>
       </c>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="H36" s="44"/>
     </row>
-    <row r="37" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" s="25" customFormat="1">
       <c r="A37" s="25" t="b">
         <v>1</v>
       </c>
@@ -15204,10 +15204,10 @@
       </c>
       <c r="H37" s="44"/>
     </row>
-    <row r="38" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" s="25" customFormat="1">
       <c r="H38" s="44"/>
     </row>
-    <row r="39" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" s="25" customFormat="1">
       <c r="A39" s="25" t="b">
         <v>1</v>
       </c>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="H39" s="42"/>
     </row>
-    <row r="40" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" s="25" customFormat="1">
       <c r="A40" s="25" t="b">
         <v>0</v>
       </c>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="H40" s="42"/>
     </row>
-    <row r="41" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" s="25" customFormat="1">
       <c r="A41" s="25" t="b">
         <v>0</v>
       </c>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="H41" s="42"/>
     </row>
-    <row r="42" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" s="25" customFormat="1">
       <c r="A42" s="25" t="b">
         <v>0</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" s="25" customFormat="1">
       <c r="A43" s="25" t="b">
         <v>1</v>
       </c>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="H43" s="42"/>
     </row>
-    <row r="44" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" s="25" customFormat="1">
       <c r="A44" s="25" t="b">
         <v>0</v>
       </c>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="H44" s="42"/>
     </row>
-    <row r="45" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" s="25" customFormat="1">
       <c r="A45" s="25" t="b">
         <v>0</v>
       </c>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="H45" s="42"/>
     </row>
-    <row r="46" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" s="25" customFormat="1">
       <c r="A46" s="25" t="b">
         <v>0</v>
       </c>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="H46" s="42"/>
     </row>
-    <row r="47" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" s="25" customFormat="1">
       <c r="A47" s="25" t="b">
         <v>0</v>
       </c>
@@ -15361,7 +15361,7 @@
       </c>
       <c r="H47" s="42"/>
     </row>
-    <row r="48" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" s="25" customFormat="1">
       <c r="A48" s="25" t="b">
         <v>0</v>
       </c>
@@ -15376,10 +15376,10 @@
       </c>
       <c r="H48" s="42"/>
     </row>
-    <row r="49" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" s="25" customFormat="1">
       <c r="H49" s="42"/>
     </row>
-    <row r="50" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" s="25" customFormat="1">
       <c r="A50" s="25" t="b">
         <v>0</v>
       </c>
@@ -15400,7 +15400,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" s="25" customFormat="1">
       <c r="A51" s="25" t="b">
         <v>1</v>
       </c>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="H51" s="42"/>
     </row>
-    <row r="52" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" s="25" customFormat="1">
       <c r="A52" s="25" t="b">
         <v>1</v>
       </c>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="H52" s="42"/>
     </row>
-    <row r="53" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" s="25" customFormat="1">
       <c r="A53" s="25" t="b">
         <v>1</v>
       </c>
@@ -15464,10 +15464,10 @@
       </c>
       <c r="H53" s="42"/>
     </row>
-    <row r="54" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" s="25" customFormat="1">
       <c r="H54" s="42"/>
     </row>
-    <row r="55" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" s="25" customFormat="1">
       <c r="A55" s="25" t="b">
         <v>1</v>
       </c>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="H55" s="42"/>
     </row>
-    <row r="56" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" s="25" customFormat="1">
       <c r="A56" s="25" t="b">
         <v>1</v>
       </c>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="H56" s="42"/>
     </row>
-    <row r="57" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" s="25" customFormat="1">
       <c r="A57" s="25" t="b">
         <v>1</v>
       </c>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="H57" s="42"/>
     </row>
-    <row r="58" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" s="25" customFormat="1">
       <c r="A58" s="25" t="b">
         <v>1</v>
       </c>
@@ -15553,7 +15553,7 @@
       <c r="H58" s="42"/>
       <c r="K58" s="17"/>
     </row>
-    <row r="59" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" s="25" customFormat="1">
       <c r="A59" s="25" t="b">
         <v>1</v>
       </c>
@@ -15575,10 +15575,10 @@
       <c r="H59" s="42"/>
       <c r="K59" s="17"/>
     </row>
-    <row r="60" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" s="25" customFormat="1">
       <c r="H60" s="42"/>
     </row>
-    <row r="61" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" s="25" customFormat="1">
       <c r="A61" s="25" t="b">
         <v>1</v>
       </c>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="H61" s="42"/>
     </row>
-    <row r="62" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" s="25" customFormat="1">
       <c r="A62" s="25" t="b">
         <v>1</v>
       </c>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H62" s="42"/>
     </row>
-    <row r="63" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" s="25" customFormat="1">
       <c r="A63" s="25" t="b">
         <v>0</v>
       </c>
@@ -15641,10 +15641,10 @@
         <v>877</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" s="25" customFormat="1">
       <c r="H64" s="42"/>
     </row>
-    <row r="65" spans="1:11" s="25" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" s="25" customFormat="1" ht="16" customHeight="1">
       <c r="A65" s="25" t="b">
         <v>1</v>
       </c>
@@ -15662,7 +15662,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="66" spans="1:11" s="25" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" s="25" customFormat="1" ht="16" customHeight="1">
       <c r="A66" s="25" t="b">
         <v>1</v>
       </c>
@@ -15681,7 +15681,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="67" spans="1:11" s="25" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" s="25" customFormat="1" ht="16" customHeight="1">
       <c r="A67" s="25" t="b">
         <v>1</v>
       </c>
@@ -15699,7 +15699,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="25" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" s="25" customFormat="1" ht="17" customHeight="1">
       <c r="A68" s="25" t="b">
         <v>1</v>
       </c>
@@ -15720,7 +15720,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" s="25" customFormat="1">
       <c r="A69" s="25" t="b">
         <v>1</v>
       </c>
@@ -15740,7 +15740,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="70" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" s="25" customFormat="1">
       <c r="A70" s="25" t="b">
         <v>1</v>
       </c>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="H70" s="42"/>
     </row>
-    <row r="71" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" s="25" customFormat="1">
       <c r="A71" s="25" t="b">
         <v>1</v>
       </c>
@@ -15783,7 +15783,7 @@
       <c r="H71" s="42"/>
       <c r="K71" s="17"/>
     </row>
-    <row r="72" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" s="25" customFormat="1">
       <c r="A72" s="25" t="b">
         <v>1</v>
       </c>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="H72" s="42"/>
     </row>
-    <row r="73" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" s="25" customFormat="1">
       <c r="A73" s="25" t="b">
         <v>1</v>
       </c>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="H73" s="42"/>
     </row>
-    <row r="74" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" s="25" customFormat="1">
       <c r="A74" s="25" t="b">
         <v>1</v>
       </c>
@@ -15846,10 +15846,10 @@
       </c>
       <c r="H74" s="42"/>
     </row>
-    <row r="75" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" s="25" customFormat="1">
       <c r="H75" s="42"/>
     </row>
-    <row r="76" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" s="25" customFormat="1">
       <c r="A76" s="25" t="b">
         <v>1</v>
       </c>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="H76" s="42"/>
     </row>
-    <row r="77" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" s="25" customFormat="1">
       <c r="A77" s="25" t="b">
         <v>1</v>
       </c>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="H77" s="42"/>
     </row>
-    <row r="78" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" s="25" customFormat="1">
       <c r="A78" s="25" t="b">
         <v>1</v>
       </c>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="H78" s="42"/>
     </row>
-    <row r="79" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" s="25" customFormat="1">
       <c r="A79" s="25" t="b">
         <v>1</v>
       </c>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="H79" s="42"/>
     </row>
-    <row r="80" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" s="25" customFormat="1">
       <c r="A80" s="25" t="b">
         <v>1</v>
       </c>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="H80" s="42"/>
     </row>
-    <row r="81" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" s="25" customFormat="1">
       <c r="A81" s="25" t="b">
         <v>1</v>
       </c>
@@ -15991,7 +15991,7 @@
       </c>
       <c r="H81" s="42"/>
     </row>
-    <row r="82" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" s="25" customFormat="1">
       <c r="A82" s="25" t="b">
         <v>1</v>
       </c>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="H82" s="42"/>
     </row>
-    <row r="83" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" s="25" customFormat="1">
       <c r="A83" s="25" t="b">
         <v>1</v>
       </c>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="H83" s="42"/>
     </row>
-    <row r="84" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" s="25" customFormat="1">
       <c r="A84" s="25" t="b">
         <v>1</v>
       </c>
@@ -16063,11 +16063,11 @@
       </c>
       <c r="H84" s="42"/>
     </row>
-    <row r="85" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" s="25" customFormat="1">
       <c r="D85" s="30"/>
       <c r="H85" s="42"/>
     </row>
-    <row r="86" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" s="25" customFormat="1">
       <c r="A86" s="25" t="b">
         <v>1</v>
       </c>
@@ -16087,7 +16087,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" s="25" customFormat="1">
       <c r="A87" s="25" t="b">
         <v>0</v>
       </c>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H87" s="42"/>
     </row>
-    <row r="88" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" s="25" customFormat="1">
       <c r="A88" s="25" t="b">
         <v>1</v>
       </c>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="H88" s="42"/>
     </row>
-    <row r="89" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" s="25" customFormat="1">
       <c r="A89" s="25" t="b">
         <v>1</v>
       </c>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="H89" s="42"/>
     </row>
-    <row r="90" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" s="25" customFormat="1">
       <c r="A90" s="25" t="b">
         <v>1</v>
       </c>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="H90" s="42"/>
     </row>
-    <row r="91" spans="1:10" s="25" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" s="25" customFormat="1" ht="17" customHeight="1">
       <c r="A91" s="25" t="b">
         <v>1</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" s="25" customFormat="1">
       <c r="A92" s="25" t="b">
         <v>1</v>
       </c>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="H92" s="42"/>
     </row>
-    <row r="93" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" s="25" customFormat="1">
       <c r="A93" s="25" t="b">
         <v>0</v>
       </c>
@@ -16235,7 +16235,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="94" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" s="25" customFormat="1">
       <c r="A94" s="25" t="b">
         <v>1</v>
       </c>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="H94" s="42"/>
     </row>
-    <row r="95" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" s="25" customFormat="1">
       <c r="A95" s="25" t="b">
         <v>1</v>
       </c>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="H95" s="42"/>
     </row>
-    <row r="96" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" s="25" customFormat="1">
       <c r="A96" s="25" t="b">
         <v>0</v>
       </c>
@@ -16298,7 +16298,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="17" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" s="17" customFormat="1" ht="17" customHeight="1">
       <c r="A97" s="25" t="b">
         <v>1</v>
       </c>
@@ -16324,7 +16324,7 @@
       <c r="I97" s="25"/>
       <c r="J97" s="25"/>
     </row>
-    <row r="98" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" s="25" customFormat="1">
       <c r="A98" s="25" t="b">
         <v>1</v>
       </c>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H98" s="42"/>
     </row>
-    <row r="99" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" s="25" customFormat="1">
       <c r="A99" s="25" t="b">
         <v>1</v>
       </c>
@@ -16372,7 +16372,7 @@
       </c>
       <c r="H99" s="42"/>
     </row>
-    <row r="100" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" s="25" customFormat="1">
       <c r="A100" s="25" t="b">
         <v>1</v>
       </c>
@@ -16396,7 +16396,7 @@
       </c>
       <c r="H100" s="42"/>
     </row>
-    <row r="101" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" s="25" customFormat="1">
       <c r="A101" s="25" t="b">
         <v>1</v>
       </c>
@@ -16420,7 +16420,7 @@
       </c>
       <c r="H101" s="42"/>
     </row>
-    <row r="102" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" s="25" customFormat="1">
       <c r="A102" s="25" t="b">
         <v>1</v>
       </c>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="H102" s="42"/>
     </row>
-    <row r="103" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" s="25" customFormat="1">
       <c r="A103" s="25" t="b">
         <v>1</v>
       </c>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="H103" s="42"/>
     </row>
-    <row r="104" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" s="25" customFormat="1">
       <c r="A104" s="25" t="b">
         <v>1</v>
       </c>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="H104" s="42"/>
     </row>
-    <row r="105" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" s="25" customFormat="1">
       <c r="A105" s="25" t="b">
         <v>1</v>
       </c>
@@ -16516,7 +16516,7 @@
       </c>
       <c r="H105" s="42"/>
     </row>
-    <row r="106" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" s="25" customFormat="1">
       <c r="A106" s="25" t="b">
         <v>1</v>
       </c>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="H106" s="42"/>
     </row>
-    <row r="107" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" s="25" customFormat="1">
       <c r="A107" s="25" t="b">
         <v>1</v>
       </c>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="H107" s="42"/>
     </row>
-    <row r="108" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" s="25" customFormat="1">
       <c r="A108" s="25" t="b">
         <v>1</v>
       </c>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="H108" s="42"/>
     </row>
-    <row r="109" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" s="25" customFormat="1">
       <c r="A109" s="25" t="b">
         <v>1</v>
       </c>
@@ -16612,7 +16612,7 @@
       </c>
       <c r="H109" s="42"/>
     </row>
-    <row r="110" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" s="25" customFormat="1">
       <c r="A110" s="25" t="b">
         <v>1</v>
       </c>
@@ -16636,7 +16636,7 @@
       </c>
       <c r="H110" s="42"/>
     </row>
-    <row r="111" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" s="25" customFormat="1">
       <c r="A111" s="25" t="b">
         <v>1</v>
       </c>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="H111" s="42"/>
     </row>
-    <row r="112" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" s="25" customFormat="1">
       <c r="A112" s="25" t="b">
         <v>1</v>
       </c>
@@ -16695,7 +16695,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}">
   <dimension ref="A1:T28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.5" bestFit="1" customWidth="1"/>
@@ -16715,7 +16715,7 @@
     <col min="20" max="20" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="37" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="37" customFormat="1" ht="19">
       <c r="A1" s="37" t="s">
         <v>666</v>
       </c>
@@ -16777,7 +16777,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" s="25" customFormat="1">
       <c r="A2" s="25" t="b">
         <v>1</v>
       </c>
@@ -16813,7 +16813,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" s="25" customFormat="1">
       <c r="A3" s="25" t="b">
         <v>1</v>
       </c>
@@ -16849,7 +16849,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" s="25" customFormat="1">
       <c r="A4" s="25" t="b">
         <v>1</v>
       </c>
@@ -16885,7 +16885,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" s="25" customFormat="1">
       <c r="A5" s="25" t="b">
         <v>1</v>
       </c>
@@ -16921,7 +16921,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" s="25" customFormat="1">
       <c r="A6" s="25" t="b">
         <v>1</v>
       </c>
@@ -16957,7 +16957,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" s="25" customFormat="1">
       <c r="A7" s="25" t="b">
         <v>1</v>
       </c>
@@ -16993,7 +16993,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" s="25" customFormat="1">
       <c r="A8" s="25" t="b">
         <v>1</v>
       </c>
@@ -17029,7 +17029,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" s="25" customFormat="1">
       <c r="A9" s="25" t="b">
         <v>1</v>
       </c>
@@ -17068,7 +17068,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="10" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" s="25" customFormat="1">
       <c r="A10" s="25" t="b">
         <v>1</v>
       </c>
@@ -17107,7 +17107,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" s="25" customFormat="1">
       <c r="A11" s="25" t="b">
         <v>1</v>
       </c>
@@ -17143,7 +17143,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" s="25" customFormat="1">
       <c r="A12" s="25" t="b">
         <v>1</v>
       </c>
@@ -17177,7 +17177,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" s="25" customFormat="1">
       <c r="A13" s="25" t="b">
         <v>1</v>
       </c>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" s="25" customFormat="1">
       <c r="A14" s="25" t="b">
         <v>1</v>
       </c>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="G14"/>
     </row>
-    <row r="15" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" s="25" customFormat="1">
       <c r="A15" s="25" t="b">
         <v>1</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="16" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" s="25" customFormat="1">
       <c r="A16" s="25" t="b">
         <v>1</v>
       </c>
@@ -17301,7 +17301,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" s="25" customFormat="1">
       <c r="A17" s="25" t="b">
         <v>1</v>
       </c>
@@ -17343,7 +17343,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" s="25" customFormat="1">
       <c r="A18" s="25" t="b">
         <v>1</v>
       </c>
@@ -17382,7 +17382,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" s="25" customFormat="1">
       <c r="A19" s="25" t="b">
         <v>1</v>
       </c>
@@ -17421,7 +17421,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" s="25" customFormat="1">
       <c r="A20" s="25" t="b">
         <v>1</v>
       </c>
@@ -17460,7 +17460,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" s="25" customFormat="1">
       <c r="A21" s="25" t="b">
         <v>1</v>
       </c>
@@ -17496,7 +17496,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" s="25" customFormat="1">
       <c r="A22" s="25" t="b">
         <v>1</v>
       </c>
@@ -17529,7 +17529,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" s="25" customFormat="1">
       <c r="A23" s="25" t="b">
         <v>1</v>
       </c>
@@ -17565,7 +17565,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" s="25" customFormat="1">
       <c r="A24" s="25" t="b">
         <v>1</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" s="25" customFormat="1">
       <c r="A25" s="25" t="b">
         <v>1</v>
       </c>
@@ -17638,7 +17638,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" s="25" customFormat="1">
       <c r="A26" s="25" t="b">
         <v>1</v>
       </c>
@@ -17674,11 +17674,11 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" s="25" customFormat="1">
       <c r="G27"/>
       <c r="H27"/>
     </row>
-    <row r="28" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" s="25" customFormat="1">
       <c r="G28"/>
       <c r="H28"/>
     </row>
@@ -17694,7 +17694,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4CA3B6-4765-0A43-8534-6DA7BF8A336D}">
   <dimension ref="A1:O17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -17710,7 +17710,7 @@
     <col min="14" max="14" width="35.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="37" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="37" customFormat="1" ht="19">
       <c r="A1" s="37" t="s">
         <v>666</v>
       </c>
@@ -17757,7 +17757,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="17" customHeight="1">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -17784,11 +17784,11 @@
         <v>849</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="19" customHeight="1">
       <c r="M3" s="33"/>
       <c r="N3" s="33"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -17818,7 +17818,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -17838,7 +17838,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15">
       <c r="A7" t="b">
         <v>1</v>
       </c>
@@ -17868,7 +17868,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -17888,7 +17888,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -17908,7 +17908,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15">
       <c r="A11" t="b">
         <v>1</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15">
       <c r="A12" t="b">
         <v>1</v>
       </c>
@@ -17958,7 +17958,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -17978,7 +17978,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15">
       <c r="A15" t="b">
         <v>1</v>
       </c>
@@ -18008,7 +18008,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15">
       <c r="A16" t="b">
         <v>1</v>
       </c>
@@ -18028,7 +18028,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="b">
         <v>1</v>
       </c>
@@ -18057,7 +18057,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC6A21B-0669-0743-9D12-F41DCA15CA4A}">
   <dimension ref="A1:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -18076,7 +18076,7 @@
     <col min="16" max="16" width="96.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="37" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="37" customFormat="1" ht="19">
       <c r="A1" s="37" t="s">
         <v>666</v>
       </c>
@@ -18126,7 +18126,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" s="25" customFormat="1">
       <c r="A2" s="25" t="b">
         <v>1</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" s="25" customFormat="1">
       <c r="A3" s="25" t="b">
         <v>1</v>
       </c>
@@ -18189,7 +18189,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" s="25" customFormat="1">
       <c r="A4" s="25" t="b">
         <v>1</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" s="25" customFormat="1">
       <c r="A5" s="25" t="b">
         <v>1</v>
       </c>
@@ -18255,7 +18255,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" s="25" customFormat="1">
       <c r="A6" s="25" t="b">
         <v>1</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" s="25" customFormat="1">
       <c r="A7" s="25" t="b">
         <v>1</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" s="25" customFormat="1">
       <c r="A8" s="25" t="b">
         <v>1</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" s="25" customFormat="1">
       <c r="A9" s="25" t="b">
         <v>1</v>
       </c>
@@ -18399,8 +18399,8 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" s="25" customFormat="1"/>
+    <row r="11" spans="1:16" s="25" customFormat="1">
       <c r="A11" s="25" t="b">
         <v>1</v>
       </c>
@@ -18432,7 +18432,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" s="25" customFormat="1">
       <c r="A12" s="25" t="b">
         <v>1</v>
       </c>
@@ -18461,7 +18461,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" s="25" customFormat="1">
       <c r="A13" s="25" t="b">
         <v>1</v>
       </c>
@@ -18490,7 +18490,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" s="25" customFormat="1">
       <c r="A14" s="25" t="b">
         <v>1</v>
       </c>
@@ -18519,7 +18519,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" s="25" customFormat="1">
       <c r="A15" s="25" t="b">
         <v>1</v>
       </c>
@@ -18545,7 +18545,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" s="25" customFormat="1">
       <c r="A16" s="25" t="b">
         <v>1</v>
       </c>
@@ -18574,7 +18574,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" s="25" customFormat="1">
       <c r="A17" s="25" t="b">
         <v>1</v>
       </c>
@@ -18603,7 +18603,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" s="25" customFormat="1">
       <c r="A18" s="25" t="b">
         <v>1</v>
       </c>
@@ -18632,7 +18632,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" s="25" customFormat="1">
       <c r="A19" s="25" t="b">
         <v>1</v>
       </c>
@@ -18661,7 +18661,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" s="25" customFormat="1">
       <c r="A20" s="25" t="b">
         <v>1</v>
       </c>
@@ -18690,7 +18690,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" s="25" customFormat="1">
       <c r="A21" s="25" t="b">
         <v>1</v>
       </c>
@@ -18719,7 +18719,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" s="25" customFormat="1">
       <c r="A22" s="25" t="b">
         <v>1</v>
       </c>
@@ -18748,7 +18748,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" s="25" customFormat="1">
       <c r="A23" s="25" t="b">
         <v>1</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" s="25" customFormat="1">
       <c r="A24" s="25" t="b">
         <v>1</v>
       </c>
@@ -18806,7 +18806,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="25" t="b">
         <v>1</v>
       </c>
@@ -18835,7 +18835,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" s="25" customFormat="1">
       <c r="A26" s="25" t="b">
         <v>1</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" s="25" customFormat="1">
       <c r="A27" s="25" t="b">
         <v>1</v>
       </c>
@@ -18893,7 +18893,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" s="25" customFormat="1">
       <c r="A28" s="25" t="b">
         <v>1</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" s="25" customFormat="1">
       <c r="A29" s="25" t="b">
         <v>1</v>
       </c>
@@ -18951,7 +18951,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" s="25" customFormat="1">
       <c r="A30" s="25" t="b">
         <v>1</v>
       </c>
@@ -18980,7 +18980,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" s="25" customFormat="1">
       <c r="A31" s="25" t="b">
         <v>1</v>
       </c>
@@ -19009,7 +19009,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" s="25" customFormat="1">
       <c r="A32" s="25" t="b">
         <v>1</v>
       </c>
@@ -19038,7 +19038,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" s="25" customFormat="1">
       <c r="A33" s="25" t="b">
         <v>1</v>
       </c>
@@ -19067,7 +19067,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" s="25" customFormat="1">
       <c r="A34" s="25" t="b">
         <v>1</v>
       </c>
@@ -19096,10 +19096,10 @@
         <v>645</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" s="25" customFormat="1">
       <c r="D35" s="30"/>
     </row>
-    <row r="36" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" s="25" customFormat="1">
       <c r="A36" s="25" t="b">
         <v>1</v>
       </c>
@@ -19132,7 +19132,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" s="25" customFormat="1">
       <c r="A37" s="25" t="b">
         <v>1</v>
       </c>
@@ -19161,7 +19161,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" s="25" customFormat="1">
       <c r="A38" s="25" t="b">
         <v>1</v>
       </c>
@@ -19190,7 +19190,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" s="25" customFormat="1">
       <c r="A39" s="25" t="b">
         <v>1</v>
       </c>
@@ -19219,7 +19219,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" s="25" customFormat="1">
       <c r="A40" s="25" t="b">
         <v>1</v>
       </c>
@@ -19248,7 +19248,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" s="25" customFormat="1">
       <c r="A41" s="25" t="b">
         <v>1</v>
       </c>
@@ -19277,7 +19277,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" s="25" customFormat="1">
       <c r="A42" s="25" t="b">
         <v>1</v>
       </c>
@@ -19306,7 +19306,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" s="25" customFormat="1">
       <c r="A43" s="25" t="b">
         <v>1</v>
       </c>
@@ -19335,7 +19335,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" s="25" customFormat="1">
       <c r="A44" s="25" t="b">
         <v>1</v>
       </c>
@@ -19364,7 +19364,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" s="25" customFormat="1">
       <c r="A45" s="25" t="b">
         <v>1</v>
       </c>
@@ -19393,7 +19393,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" s="25" customFormat="1">
       <c r="A46" s="25" t="b">
         <v>1</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" s="25" customFormat="1">
       <c r="A47" s="25" t="b">
         <v>1</v>
       </c>
@@ -19451,7 +19451,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" s="25" customFormat="1">
       <c r="A48" s="25" t="b">
         <v>1</v>
       </c>
@@ -19480,7 +19480,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" s="25" customFormat="1">
       <c r="A49" s="25" t="b">
         <v>1</v>
       </c>
@@ -19509,7 +19509,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" s="25" customFormat="1">
       <c r="A50" s="25" t="b">
         <v>1</v>
       </c>
@@ -19538,7 +19538,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" s="25" customFormat="1">
       <c r="A51" s="25" t="b">
         <v>1</v>
       </c>
@@ -19567,7 +19567,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" s="25" customFormat="1">
       <c r="A52" s="25" t="b">
         <v>1</v>
       </c>
@@ -19596,7 +19596,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" s="25" customFormat="1">
       <c r="A53" s="25" t="b">
         <v>1</v>
       </c>
@@ -19625,7 +19625,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" s="25" customFormat="1">
       <c r="A54" s="25" t="b">
         <v>1</v>
       </c>
@@ -19654,7 +19654,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" s="25" customFormat="1">
       <c r="A55" s="25" t="b">
         <v>1</v>
       </c>
@@ -19683,7 +19683,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" s="25" customFormat="1">
       <c r="A56" s="25" t="b">
         <v>1</v>
       </c>
@@ -19712,7 +19712,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" s="25" customFormat="1">
       <c r="A57" s="25" t="b">
         <v>1</v>
       </c>
@@ -19741,7 +19741,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" s="25" customFormat="1">
       <c r="A58" s="25" t="b">
         <v>1</v>
       </c>
@@ -19770,7 +19770,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" s="25" customFormat="1">
       <c r="A59" s="25" t="b">
         <v>1</v>
       </c>
@@ -19799,7 +19799,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" s="25" customFormat="1">
       <c r="A60" s="25" t="b">
         <v>1</v>
       </c>
@@ -19828,7 +19828,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" s="25" customFormat="1">
       <c r="A61" s="25" t="b">
         <v>1</v>
       </c>
@@ -19857,7 +19857,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" s="25" customFormat="1">
       <c r="A62" s="25" t="b">
         <v>1</v>
       </c>
@@ -19886,7 +19886,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="63" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" s="25" customFormat="1">
       <c r="A63" s="25" t="b">
         <v>1</v>
       </c>
@@ -19915,7 +19915,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="64" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" s="25" customFormat="1">
       <c r="A64" s="25" t="b">
         <v>1</v>
       </c>
@@ -19944,7 +19944,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="65" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" s="25" customFormat="1">
       <c r="A65" s="25" t="b">
         <v>1</v>
       </c>
@@ -19973,7 +19973,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="66" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" s="25" customFormat="1">
       <c r="A66" s="25" t="b">
         <v>1</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="67" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" s="25" customFormat="1">
       <c r="A67" s="25" t="b">
         <v>1</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" s="25" customFormat="1">
       <c r="A68" s="25" t="b">
         <v>1</v>
       </c>
@@ -20060,10 +20060,10 @@
         <v>645</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" s="25" customFormat="1">
       <c r="D69" s="35"/>
     </row>
-    <row r="70" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" s="25" customFormat="1">
       <c r="A70" s="25" t="b">
         <v>1</v>
       </c>
@@ -20096,7 +20096,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="71" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" s="25" customFormat="1">
       <c r="A71" s="25" t="b">
         <v>1</v>
       </c>
@@ -20125,7 +20125,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="72" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" s="25" customFormat="1">
       <c r="A72" s="25" t="b">
         <v>1</v>
       </c>
@@ -20154,7 +20154,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="73" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" s="25" customFormat="1">
       <c r="A73" s="25" t="b">
         <v>1</v>
       </c>
@@ -20183,7 +20183,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" s="25" customFormat="1">
       <c r="A74" s="25" t="b">
         <v>1</v>
       </c>
@@ -20212,7 +20212,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="75" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" s="25" customFormat="1">
       <c r="A75" s="25" t="b">
         <v>1</v>
       </c>
@@ -20241,7 +20241,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="76" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" s="25" customFormat="1">
       <c r="A76" s="25" t="b">
         <v>1</v>
       </c>
@@ -20270,10 +20270,10 @@
         <v>645</v>
       </c>
     </row>
-    <row r="77" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" s="25" customFormat="1">
       <c r="D77" s="30"/>
     </row>
-    <row r="78" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" s="25" customFormat="1">
       <c r="A78" s="25" t="b">
         <v>1</v>
       </c>
@@ -20309,7 +20309,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="79" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" s="25" customFormat="1">
       <c r="A79" s="25" t="b">
         <v>1</v>
       </c>
@@ -20340,12 +20340,12 @@
         <v>645</v>
       </c>
     </row>
-    <row r="80" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" s="25" customFormat="1">
       <c r="D80" s="30"/>
       <c r="H80" s="26"/>
       <c r="I80" s="26"/>
     </row>
-    <row r="81" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" s="25" customFormat="1">
       <c r="A81" s="25" t="b">
         <v>1</v>
       </c>
@@ -20375,7 +20375,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" s="25" customFormat="1">
       <c r="A82" s="25" t="b">
         <v>1</v>
       </c>
@@ -20404,7 +20404,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" s="25" customFormat="1">
       <c r="A83" s="25" t="b">
         <v>1</v>
       </c>
@@ -20433,7 +20433,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="84" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" s="25" customFormat="1">
       <c r="A84" s="25" t="b">
         <v>1</v>
       </c>
@@ -20462,7 +20462,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" s="25" customFormat="1">
       <c r="A85" s="25" t="b">
         <v>1</v>
       </c>
@@ -20491,7 +20491,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" s="25" customFormat="1">
       <c r="A86" s="25" t="b">
         <v>1</v>
       </c>
@@ -20520,7 +20520,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" s="25" customFormat="1">
       <c r="A87" s="25" t="b">
         <v>1</v>
       </c>
@@ -20549,10 +20549,10 @@
         <v>645</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" s="25" customFormat="1">
       <c r="D88" s="30"/>
     </row>
-    <row r="89" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" s="25" customFormat="1">
       <c r="A89" s="25" t="b">
         <v>1</v>
       </c>
@@ -20582,7 +20582,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" s="25" customFormat="1">
       <c r="A90" s="25" t="b">
         <v>1</v>
       </c>
@@ -20611,7 +20611,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" s="25" customFormat="1">
       <c r="A91" s="25" t="b">
         <v>1</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" s="25" customFormat="1">
       <c r="A92" s="25" t="b">
         <v>1</v>
       </c>
@@ -20669,7 +20669,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" s="25" customFormat="1">
       <c r="A93" s="25" t="b">
         <v>1</v>
       </c>
@@ -20698,7 +20698,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" s="25" customFormat="1">
       <c r="A94" s="25" t="b">
         <v>1</v>
       </c>
@@ -20727,7 +20727,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" s="25" customFormat="1">
       <c r="A95" s="25" t="b">
         <v>1</v>
       </c>
@@ -20756,7 +20756,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" s="25" customFormat="1">
       <c r="A96" s="25" t="b">
         <v>1</v>
       </c>
@@ -20785,7 +20785,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="97" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" s="25" customFormat="1">
       <c r="A97" s="25" t="b">
         <v>1</v>
       </c>
@@ -20814,7 +20814,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="98" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" s="25" customFormat="1">
       <c r="A98" s="25" t="b">
         <v>1</v>
       </c>
@@ -20843,7 +20843,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="99" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" s="25" customFormat="1">
       <c r="A99" s="25" t="b">
         <v>1</v>
       </c>
@@ -20872,7 +20872,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="100" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" s="25" customFormat="1">
       <c r="A100" s="25" t="b">
         <v>1</v>
       </c>
@@ -20901,7 +20901,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="101" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" s="25" customFormat="1">
       <c r="A101" s="25" t="b">
         <v>1</v>
       </c>
@@ -20930,7 +20930,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="102" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" s="25" customFormat="1">
       <c r="A102" s="25" t="b">
         <v>1</v>
       </c>
@@ -20959,7 +20959,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="103" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" s="25" customFormat="1">
       <c r="A103" s="25" t="b">
         <v>1</v>
       </c>
@@ -20988,7 +20988,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="104" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" s="25" customFormat="1">
       <c r="A104" s="25" t="b">
         <v>1</v>
       </c>
@@ -21017,10 +21017,10 @@
         <v>645</v>
       </c>
     </row>
-    <row r="105" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" s="25" customFormat="1">
       <c r="D105" s="30"/>
     </row>
-    <row r="106" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" s="25" customFormat="1">
       <c r="A106" s="25" t="b">
         <v>1</v>
       </c>
@@ -21052,7 +21052,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="107" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" s="25" customFormat="1">
       <c r="A107" s="25" t="b">
         <v>1</v>
       </c>
@@ -21081,7 +21081,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="108" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" s="25" customFormat="1">
       <c r="A108" s="25" t="b">
         <v>1</v>
       </c>
@@ -21110,7 +21110,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="109" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" s="25" customFormat="1">
       <c r="A109" s="25" t="b">
         <v>1</v>
       </c>
@@ -21139,7 +21139,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="110" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" s="25" customFormat="1">
       <c r="A110" s="25" t="b">
         <v>1</v>
       </c>
@@ -21173,7 +21173,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F8335C-0B7A-174C-9395-80905662B1F5}">
   <dimension ref="A1:Q16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -21192,7 +21192,7 @@
     <col min="17" max="17" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="37" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="37" customFormat="1" ht="19">
       <c r="A1" s="37" t="s">
         <v>666</v>
       </c>
@@ -21245,7 +21245,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -21277,7 +21277,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -21309,7 +21309,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -21341,7 +21341,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -21373,7 +21373,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -21405,7 +21405,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17">
       <c r="A7" t="b">
         <v>1</v>
       </c>
@@ -21437,7 +21437,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -21469,7 +21469,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -21501,7 +21501,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17">
       <c r="A10" t="b">
         <v>1</v>
       </c>
@@ -21533,7 +21533,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17">
       <c r="A11" t="b">
         <v>1</v>
       </c>
@@ -21565,7 +21565,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17">
       <c r="A12" t="b">
         <v>1</v>
       </c>
@@ -21597,7 +21597,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -21629,7 +21629,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17">
       <c r="A14" t="b">
         <v>1</v>
       </c>
@@ -21661,7 +21661,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17">
       <c r="A15" t="b">
         <v>1</v>
       </c>
@@ -21693,7 +21693,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17">
       <c r="A16" t="b">
         <v>1</v>
       </c>
@@ -21734,7 +21734,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC10C3F-0C27-5546-8767-E60C7CACEA9D}">
   <dimension ref="A1:J191"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
@@ -21747,7 +21747,7 @@
     <col min="10" max="10" width="62.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="37" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="37" customFormat="1" ht="19">
       <c r="A1" s="37" t="s">
         <v>666</v>
       </c>
@@ -21779,7 +21779,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -21796,7 +21796,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -21810,7 +21810,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -21824,7 +21824,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -21838,7 +21838,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -21852,7 +21852,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -21869,7 +21869,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -21883,7 +21883,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" t="b">
         <v>1</v>
       </c>
@@ -21897,7 +21897,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" t="b">
         <v>1</v>
       </c>
@@ -21911,7 +21911,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" t="b">
         <v>1</v>
       </c>
@@ -21925,7 +21925,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -21939,7 +21939,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" t="b">
         <v>1</v>
       </c>
@@ -21953,7 +21953,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" t="b">
         <v>1</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" t="b">
         <v>1</v>
       </c>
@@ -21984,7 +21984,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" t="b">
         <v>1</v>
       </c>
@@ -21998,7 +21998,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" t="b">
         <v>1</v>
       </c>
@@ -22012,7 +22012,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" t="b">
         <v>1</v>
       </c>
@@ -22026,7 +22026,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" t="b">
         <v>1</v>
       </c>
@@ -22040,7 +22040,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" t="b">
         <v>1</v>
       </c>
@@ -22054,7 +22054,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" t="b">
         <v>1</v>
       </c>
@@ -22068,7 +22068,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" t="b">
         <v>1</v>
       </c>
@@ -22082,7 +22082,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" t="b">
         <v>1</v>
       </c>
@@ -22096,7 +22096,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" t="b">
         <v>1</v>
       </c>
@@ -22110,7 +22110,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" t="b">
         <v>1</v>
       </c>
@@ -22124,7 +22124,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" t="b">
         <v>1</v>
       </c>
@@ -22141,7 +22141,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" t="b">
         <v>1</v>
       </c>
@@ -22155,7 +22155,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" t="b">
         <v>1</v>
       </c>
@@ -22169,7 +22169,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" t="b">
         <v>1</v>
       </c>
@@ -22183,7 +22183,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" t="b">
         <v>1</v>
       </c>
@@ -22197,7 +22197,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" t="b">
         <v>1</v>
       </c>
@@ -22211,7 +22211,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" t="b">
         <v>1</v>
       </c>
@@ -22225,7 +22225,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" t="b">
         <v>1</v>
       </c>
@@ -22239,7 +22239,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" t="b">
         <v>1</v>
       </c>
@@ -22253,7 +22253,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" t="b">
         <v>1</v>
       </c>
@@ -22267,7 +22267,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10">
       <c r="A39" t="b">
         <v>1</v>
       </c>
@@ -22281,7 +22281,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10">
       <c r="A40" t="b">
         <v>1</v>
       </c>
@@ -22295,7 +22295,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10">
       <c r="A41" t="b">
         <v>1</v>
       </c>
@@ -22309,7 +22309,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10">
       <c r="A43" t="b">
         <v>1</v>
       </c>
@@ -22326,7 +22326,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10">
       <c r="A44" t="b">
         <v>1</v>
       </c>
@@ -22340,7 +22340,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10">
       <c r="A45" t="b">
         <v>1</v>
       </c>
@@ -22354,7 +22354,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="A46" t="b">
         <v>1</v>
       </c>
@@ -22368,7 +22368,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10">
       <c r="A47" t="b">
         <v>1</v>
       </c>
@@ -22382,7 +22382,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10">
       <c r="A48" t="b">
         <v>1</v>
       </c>
@@ -22396,7 +22396,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10">
       <c r="A49" t="b">
         <v>1</v>
       </c>
@@ -22410,7 +22410,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10">
       <c r="A50" t="b">
         <v>1</v>
       </c>
@@ -22424,7 +22424,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10">
       <c r="A51" t="b">
         <v>1</v>
       </c>
@@ -22438,7 +22438,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52" t="b">
         <v>1</v>
       </c>
@@ -22452,7 +22452,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10">
       <c r="A53" t="b">
         <v>1</v>
       </c>
@@ -22466,7 +22466,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10">
       <c r="A55" t="b">
         <v>1</v>
       </c>
@@ -22484,7 +22484,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="A56" t="b">
         <v>1</v>
       </c>
@@ -22498,7 +22498,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="A57" t="b">
         <v>1</v>
       </c>
@@ -22512,7 +22512,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="A58" t="b">
         <v>1</v>
       </c>
@@ -22526,7 +22526,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10">
       <c r="A59" t="b">
         <v>1</v>
       </c>
@@ -22540,7 +22540,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10">
       <c r="A60" t="b">
         <v>1</v>
       </c>
@@ -22554,7 +22554,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10">
       <c r="A61" t="b">
         <v>1</v>
       </c>
@@ -22568,7 +22568,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10">
       <c r="A62" t="b">
         <v>1</v>
       </c>
@@ -22582,7 +22582,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10">
       <c r="A63" t="b">
         <v>1</v>
       </c>
@@ -22596,7 +22596,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10">
       <c r="A64" t="b">
         <v>1</v>
       </c>
@@ -22610,7 +22610,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" t="b">
         <v>1</v>
       </c>
@@ -22624,7 +22624,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" t="b">
         <v>1</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" t="b">
         <v>1</v>
       </c>
@@ -22652,7 +22652,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" t="b">
         <v>1</v>
       </c>
@@ -22666,7 +22666,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" t="b">
         <v>1</v>
       </c>
@@ -22680,7 +22680,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9">
       <c r="A70" t="b">
         <v>1</v>
       </c>
@@ -22694,7 +22694,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9">
       <c r="A71" t="b">
         <v>1</v>
       </c>
@@ -22708,7 +22708,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9">
       <c r="A72" t="b">
         <v>1</v>
       </c>
@@ -22722,7 +22722,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9">
       <c r="A73" t="b">
         <v>1</v>
       </c>
@@ -22736,7 +22736,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9">
       <c r="A74" t="b">
         <v>1</v>
       </c>
@@ -22750,7 +22750,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9">
       <c r="A75" t="b">
         <v>1</v>
       </c>
@@ -22764,7 +22764,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9">
       <c r="A76" t="b">
         <v>1</v>
       </c>
@@ -22778,7 +22778,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9">
       <c r="A77" t="b">
         <v>1</v>
       </c>
@@ -22792,7 +22792,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9">
       <c r="A78" t="b">
         <v>1</v>
       </c>
@@ -22806,7 +22806,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9">
       <c r="A79" t="b">
         <v>1</v>
       </c>
@@ -22820,7 +22820,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9">
       <c r="A80" t="b">
         <v>1</v>
       </c>
@@ -22834,7 +22834,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9">
       <c r="A81" t="b">
         <v>1</v>
       </c>
@@ -22848,7 +22848,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9">
       <c r="A82" t="b">
         <v>1</v>
       </c>
@@ -22862,7 +22862,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9">
       <c r="A83" t="b">
         <v>1</v>
       </c>
@@ -22876,7 +22876,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9">
       <c r="A84" t="b">
         <v>1</v>
       </c>
@@ -22890,7 +22890,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9">
       <c r="A85" t="b">
         <v>1</v>
       </c>
@@ -22904,7 +22904,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9">
       <c r="A86" t="b">
         <v>1</v>
       </c>
@@ -22918,7 +22918,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9">
       <c r="A87" t="b">
         <v>1</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9">
       <c r="A88" t="b">
         <v>1</v>
       </c>
@@ -22946,7 +22946,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9">
       <c r="A89" t="b">
         <v>1</v>
       </c>
@@ -22960,7 +22960,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9">
       <c r="A90" t="b">
         <v>1</v>
       </c>
@@ -22974,7 +22974,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9">
       <c r="A91" t="b">
         <v>1</v>
       </c>
@@ -22988,7 +22988,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9">
       <c r="A92" t="b">
         <v>1</v>
       </c>
@@ -23002,7 +23002,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9">
       <c r="A93" t="b">
         <v>1</v>
       </c>
@@ -23016,7 +23016,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9">
       <c r="A94" t="b">
         <v>1</v>
       </c>
@@ -23030,7 +23030,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9">
       <c r="A95" t="b">
         <v>1</v>
       </c>
@@ -23044,7 +23044,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9">
       <c r="A96" t="b">
         <v>1</v>
       </c>
@@ -23058,7 +23058,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9">
       <c r="A97" t="b">
         <v>1</v>
       </c>
@@ -23072,7 +23072,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9">
       <c r="A98" t="b">
         <v>1</v>
       </c>
@@ -23086,7 +23086,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9">
       <c r="A99" t="b">
         <v>1</v>
       </c>
@@ -23100,7 +23100,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9">
       <c r="A100" t="b">
         <v>1</v>
       </c>
@@ -23114,7 +23114,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9">
       <c r="A101" t="b">
         <v>1</v>
       </c>
@@ -23128,7 +23128,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9">
       <c r="A102" t="b">
         <v>1</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9">
       <c r="A103" t="b">
         <v>1</v>
       </c>
@@ -23156,7 +23156,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9">
       <c r="A104" t="b">
         <v>1</v>
       </c>
@@ -23170,7 +23170,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9">
       <c r="A105" t="b">
         <v>1</v>
       </c>
@@ -23184,7 +23184,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9">
       <c r="A106" t="b">
         <v>1</v>
       </c>
@@ -23198,7 +23198,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9">
       <c r="A107" t="b">
         <v>1</v>
       </c>
@@ -23212,7 +23212,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9">
       <c r="A108" t="b">
         <v>1</v>
       </c>
@@ -23226,7 +23226,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9">
       <c r="A109" t="b">
         <v>1</v>
       </c>
@@ -23240,7 +23240,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9">
       <c r="A110" t="b">
         <v>1</v>
       </c>
@@ -23254,7 +23254,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9">
       <c r="A111" t="b">
         <v>1</v>
       </c>
@@ -23268,7 +23268,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9">
       <c r="A112" t="b">
         <v>1</v>
       </c>
@@ -23282,7 +23282,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9">
       <c r="A113" t="b">
         <v>1</v>
       </c>
@@ -23296,7 +23296,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9">
       <c r="A114" t="b">
         <v>1</v>
       </c>
@@ -23310,7 +23310,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9">
       <c r="A115" t="b">
         <v>1</v>
       </c>
@@ -23324,7 +23324,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9">
       <c r="A116" t="b">
         <v>1</v>
       </c>
@@ -23338,7 +23338,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9">
       <c r="A117" t="b">
         <v>1</v>
       </c>
@@ -23352,7 +23352,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9">
       <c r="A118" t="b">
         <v>1</v>
       </c>
@@ -23366,7 +23366,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9">
       <c r="A119" t="b">
         <v>1</v>
       </c>
@@ -23380,7 +23380,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9">
       <c r="A120" t="b">
         <v>1</v>
       </c>
@@ -23394,7 +23394,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9">
       <c r="A121" t="b">
         <v>1</v>
       </c>
@@ -23408,7 +23408,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9">
       <c r="A122" t="b">
         <v>1</v>
       </c>
@@ -23422,7 +23422,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9">
       <c r="A123" t="b">
         <v>1</v>
       </c>
@@ -23436,7 +23436,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9">
       <c r="A124" t="b">
         <v>1</v>
       </c>
@@ -23450,7 +23450,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9">
       <c r="A125" t="b">
         <v>1</v>
       </c>
@@ -23464,7 +23464,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9">
       <c r="A126" t="b">
         <v>1</v>
       </c>
@@ -23478,7 +23478,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9">
       <c r="A127" t="b">
         <v>1</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9">
       <c r="A128" t="b">
         <v>1</v>
       </c>
@@ -23506,7 +23506,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9">
       <c r="A129" t="b">
         <v>1</v>
       </c>
@@ -23520,7 +23520,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9">
       <c r="A130" t="b">
         <v>1</v>
       </c>
@@ -23534,7 +23534,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9">
       <c r="A131" t="b">
         <v>1</v>
       </c>
@@ -23548,7 +23548,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9">
       <c r="A132" t="b">
         <v>1</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9">
       <c r="A133" t="b">
         <v>1</v>
       </c>
@@ -23576,7 +23576,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9">
       <c r="A134" t="b">
         <v>1</v>
       </c>
@@ -23590,7 +23590,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9">
       <c r="A135" t="b">
         <v>1</v>
       </c>
@@ -23604,7 +23604,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9">
       <c r="A136" t="b">
         <v>1</v>
       </c>
@@ -23618,7 +23618,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9">
       <c r="A137" t="b">
         <v>1</v>
       </c>
@@ -23632,7 +23632,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9">
       <c r="A138" t="b">
         <v>1</v>
       </c>
@@ -23646,7 +23646,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9">
       <c r="A139" t="b">
         <v>1</v>
       </c>
@@ -23660,7 +23660,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9">
       <c r="A140" t="b">
         <v>1</v>
       </c>
@@ -23674,7 +23674,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9">
       <c r="A141" t="b">
         <v>1</v>
       </c>
@@ -23688,7 +23688,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9">
       <c r="A142" t="b">
         <v>1</v>
       </c>
@@ -23702,7 +23702,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9">
       <c r="A143" t="b">
         <v>1</v>
       </c>
@@ -23716,7 +23716,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9">
       <c r="A144" t="b">
         <v>1</v>
       </c>
@@ -23730,7 +23730,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9">
       <c r="A145" t="b">
         <v>1</v>
       </c>
@@ -23744,7 +23744,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9">
       <c r="A146" t="b">
         <v>1</v>
       </c>
@@ -23758,7 +23758,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9">
       <c r="A147" t="b">
         <v>1</v>
       </c>
@@ -23772,7 +23772,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9">
       <c r="A148" t="b">
         <v>1</v>
       </c>
@@ -23786,7 +23786,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9">
       <c r="A149" t="b">
         <v>1</v>
       </c>
@@ -23800,7 +23800,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9">
       <c r="A150" t="b">
         <v>1</v>
       </c>
@@ -23814,7 +23814,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9">
       <c r="A151" t="b">
         <v>1</v>
       </c>
@@ -23828,7 +23828,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9">
       <c r="A152" t="b">
         <v>1</v>
       </c>
@@ -23842,7 +23842,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9">
       <c r="A153" t="b">
         <v>1</v>
       </c>
@@ -23856,7 +23856,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9">
       <c r="A154" t="b">
         <v>1</v>
       </c>
@@ -23870,7 +23870,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9">
       <c r="A155" t="b">
         <v>1</v>
       </c>
@@ -23884,7 +23884,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9">
       <c r="A156" t="b">
         <v>1</v>
       </c>
@@ -23898,7 +23898,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9">
       <c r="A157" t="b">
         <v>1</v>
       </c>
@@ -23912,7 +23912,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9">
       <c r="A158" t="b">
         <v>1</v>
       </c>
@@ -23926,7 +23926,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9">
       <c r="A159" t="b">
         <v>1</v>
       </c>
@@ -23940,7 +23940,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9">
       <c r="A160" t="b">
         <v>1</v>
       </c>
@@ -23954,7 +23954,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10">
       <c r="A161" t="b">
         <v>1</v>
       </c>
@@ -23968,7 +23968,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10">
       <c r="A162" t="b">
         <v>1</v>
       </c>
@@ -23982,7 +23982,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10">
       <c r="A163" t="b">
         <v>1</v>
       </c>
@@ -23996,7 +23996,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10">
       <c r="A164" t="b">
         <v>1</v>
       </c>
@@ -24010,7 +24010,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10">
       <c r="A165" t="b">
         <v>1</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10">
       <c r="A166" t="b">
         <v>1</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10">
       <c r="A167" t="b">
         <v>1</v>
       </c>
@@ -24052,7 +24052,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10">
       <c r="A168" t="b">
         <v>1</v>
       </c>
@@ -24066,7 +24066,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10">
       <c r="A169" t="b">
         <v>1</v>
       </c>
@@ -24080,7 +24080,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10">
       <c r="A170" t="b">
         <v>1</v>
       </c>
@@ -24094,7 +24094,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10">
       <c r="A172" t="b">
         <v>1</v>
       </c>
@@ -24111,7 +24111,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10">
       <c r="A173" t="b">
         <v>1</v>
       </c>
@@ -24125,7 +24125,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10">
       <c r="A174" t="b">
         <v>1</v>
       </c>
@@ -24139,7 +24139,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10">
       <c r="A175" t="b">
         <v>1</v>
       </c>
@@ -24153,7 +24153,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10">
       <c r="A176" t="b">
         <v>1</v>
       </c>
@@ -24167,7 +24167,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9">
       <c r="A177" t="b">
         <v>1</v>
       </c>
@@ -24181,7 +24181,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9">
       <c r="A178" t="b">
         <v>1</v>
       </c>
@@ -24195,7 +24195,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9">
       <c r="A179" t="b">
         <v>1</v>
       </c>
@@ -24209,7 +24209,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9">
       <c r="A180" t="b">
         <v>1</v>
       </c>
@@ -24223,7 +24223,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9">
       <c r="A181" t="b">
         <v>1</v>
       </c>
@@ -24237,7 +24237,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9">
       <c r="A182" t="b">
         <v>1</v>
       </c>
@@ -24251,7 +24251,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9">
       <c r="A183" t="b">
         <v>1</v>
       </c>
@@ -24265,7 +24265,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9">
       <c r="A184" t="b">
         <v>1</v>
       </c>
@@ -24279,7 +24279,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9">
       <c r="A185" t="b">
         <v>1</v>
       </c>
@@ -24293,7 +24293,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9">
       <c r="A186" t="b">
         <v>1</v>
       </c>
@@ -24307,7 +24307,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9">
       <c r="A187" t="b">
         <v>1</v>
       </c>
@@ -24321,7 +24321,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9">
       <c r="A188" t="b">
         <v>1</v>
       </c>
@@ -24335,7 +24335,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9">
       <c r="A189" t="b">
         <v>1</v>
       </c>
@@ -24349,7 +24349,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9">
       <c r="A190" t="b">
         <v>1</v>
       </c>
@@ -24363,7 +24363,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9">
       <c r="A191" t="b">
         <v>1</v>
       </c>
@@ -24386,7 +24386,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077DB476-AE11-E742-9E3D-7ABA37A90AEF}">
   <dimension ref="A1:J88"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
@@ -24397,7 +24397,7 @@
     <col min="9" max="9" width="96.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="17" t="s">
         <v>747</v>
       </c>
@@ -24429,7 +24429,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -24458,7 +24458,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="B3" t="s">
         <v>78</v>
       </c>
@@ -24475,7 +24475,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -24504,7 +24504,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -24530,7 +24530,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" t="b">
         <v>1</v>
       </c>
@@ -24553,7 +24553,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -24576,7 +24576,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -24596,7 +24596,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" t="b">
         <v>1</v>
       </c>
@@ -24616,7 +24616,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" t="b">
         <v>1</v>
       </c>
@@ -24636,7 +24636,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" t="b">
         <v>1</v>
       </c>
@@ -24656,7 +24656,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -24679,7 +24679,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" t="b">
         <v>1</v>
       </c>
@@ -24699,7 +24699,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" t="b">
         <v>1</v>
       </c>
@@ -24731,7 +24731,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" t="b">
         <v>1</v>
       </c>
@@ -24751,7 +24751,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" t="b">
         <v>1</v>
       </c>
@@ -24771,7 +24771,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" t="b">
         <v>1</v>
       </c>
@@ -24791,7 +24791,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" t="b">
         <v>1</v>
       </c>
@@ -24817,7 +24817,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" t="b">
         <v>1</v>
       </c>
@@ -24837,7 +24837,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" t="b">
         <v>1</v>
       </c>
@@ -24860,7 +24860,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" t="b">
         <v>1</v>
       </c>
@@ -24880,7 +24880,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" t="b">
         <v>1</v>
       </c>
@@ -24903,7 +24903,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" t="b">
         <v>1</v>
       </c>
@@ -24923,7 +24923,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" t="b">
         <v>1</v>
       </c>
@@ -24943,7 +24943,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" t="b">
         <v>1</v>
       </c>
@@ -24963,7 +24963,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" t="b">
         <v>1</v>
       </c>
@@ -24995,7 +24995,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" t="b">
         <v>1</v>
       </c>
@@ -25015,7 +25015,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" t="b">
         <v>1</v>
       </c>
@@ -25038,7 +25038,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" t="b">
         <v>1</v>
       </c>
@@ -25058,7 +25058,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" t="b">
         <v>1</v>
       </c>
@@ -25078,7 +25078,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" t="b">
         <v>1</v>
       </c>
@@ -25098,7 +25098,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" t="b">
         <v>1</v>
       </c>
@@ -25115,7 +25115,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10">
       <c r="A39" t="b">
         <v>1</v>
       </c>
@@ -25147,7 +25147,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10">
       <c r="A40" t="b">
         <v>1</v>
       </c>
@@ -25167,7 +25167,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10">
       <c r="A41" t="b">
         <v>1</v>
       </c>
@@ -25187,7 +25187,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10">
       <c r="A42" t="b">
         <v>1</v>
       </c>
@@ -25207,7 +25207,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10">
       <c r="A43" t="b">
         <v>1</v>
       </c>
@@ -25227,7 +25227,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10">
       <c r="A44" t="b">
         <v>1</v>
       </c>
@@ -25247,7 +25247,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10">
       <c r="A45" t="b">
         <v>1</v>
       </c>
@@ -25261,7 +25261,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="A46" t="b">
         <v>1</v>
       </c>
@@ -25275,7 +25275,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" s="23" customFormat="1">
       <c r="A48" s="23" t="b">
         <v>0</v>
       </c>
@@ -25304,7 +25304,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" s="23" customFormat="1">
       <c r="B49" s="23" t="s">
         <v>739</v>
       </c>
@@ -25318,7 +25318,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" s="23" customFormat="1">
       <c r="B50" s="23" t="s">
         <v>739</v>
       </c>
@@ -25332,7 +25332,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" s="23" customFormat="1">
       <c r="A52" s="23" t="b">
         <v>0</v>
       </c>
@@ -25340,7 +25340,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" s="23" customFormat="1">
       <c r="A54" s="23" t="b">
         <v>0</v>
       </c>
@@ -25354,7 +25354,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" s="23" customFormat="1">
       <c r="B55" s="23" t="s">
         <v>738</v>
       </c>
@@ -25377,7 +25377,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" s="23" customFormat="1">
       <c r="B56" s="23" t="s">
         <v>738</v>
       </c>
@@ -25388,7 +25388,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" s="23" customFormat="1">
       <c r="B57" s="23" t="s">
         <v>738</v>
       </c>
@@ -25399,7 +25399,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" s="23" customFormat="1">
       <c r="B58" s="23" t="s">
         <v>738</v>
       </c>
@@ -25410,7 +25410,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" s="23" customFormat="1">
       <c r="B59" s="23" t="s">
         <v>738</v>
       </c>
@@ -25421,7 +25421,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="61" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" s="23" customFormat="1">
       <c r="A61" s="23" t="b">
         <v>0</v>
       </c>
@@ -25447,7 +25447,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="62" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" s="23" customFormat="1">
       <c r="B62" s="23" t="s">
         <v>740</v>
       </c>
@@ -25461,7 +25461,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" s="23" customFormat="1">
       <c r="B63" s="23" t="s">
         <v>740</v>
       </c>
@@ -25475,7 +25475,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" s="23" customFormat="1">
       <c r="B64" s="23" t="s">
         <v>740</v>
       </c>
@@ -25489,7 +25489,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" s="23" customFormat="1">
       <c r="A66" s="23" t="b">
         <v>0</v>
       </c>
@@ -25497,7 +25497,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" s="23" customFormat="1">
       <c r="A68" s="23" t="b">
         <v>0</v>
       </c>
@@ -25517,7 +25517,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" s="23" customFormat="1">
       <c r="B69" s="23" t="s">
         <v>737</v>
       </c>
@@ -25531,7 +25531,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" s="23" customFormat="1">
       <c r="B70" s="23" t="s">
         <v>737</v>
       </c>
@@ -25545,7 +25545,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="71" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" s="23" customFormat="1">
       <c r="B71" s="23" t="s">
         <v>737</v>
       </c>
@@ -25559,7 +25559,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" s="23" customFormat="1">
       <c r="A73" s="23" t="b">
         <v>0</v>
       </c>
@@ -25588,7 +25588,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="74" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" s="23" customFormat="1">
       <c r="B74" s="23" t="s">
         <v>723</v>
       </c>
@@ -25602,7 +25602,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" s="23" customFormat="1">
       <c r="B75" s="23" t="s">
         <v>723</v>
       </c>
@@ -25616,7 +25616,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="77" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" s="23" customFormat="1">
       <c r="A77" s="23" t="b">
         <v>0</v>
       </c>
@@ -25639,7 +25639,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" s="23" customFormat="1">
       <c r="B78" s="23" t="s">
         <v>741</v>
       </c>
@@ -25653,7 +25653,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" s="23" customFormat="1">
       <c r="B79" s="23" t="s">
         <v>741</v>
       </c>
@@ -25667,7 +25667,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="80" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" s="23" customFormat="1">
       <c r="B80" s="23" t="s">
         <v>741</v>
       </c>
@@ -25681,7 +25681,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="82" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" s="23" customFormat="1">
       <c r="A82" s="23" t="b">
         <v>0</v>
       </c>
@@ -25689,7 +25689,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="84" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" s="23" customFormat="1">
       <c r="A84" s="23" t="b">
         <v>0</v>
       </c>
@@ -25697,7 +25697,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="86" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" s="23" customFormat="1">
       <c r="A86" s="23" t="b">
         <v>0</v>
       </c>
@@ -25705,7 +25705,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="88" spans="1:2" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" s="23" customFormat="1">
       <c r="A88" s="23" t="b">
         <v>0</v>
       </c>
@@ -25722,7 +25722,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF6C9F4-4010-9243-98AE-74EEEFFCAC53}">
   <dimension ref="A1:L87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="3" width="27.1640625" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" customWidth="1"/>
@@ -25734,7 +25734,7 @@
     <col min="12" max="12" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="18" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="18" customFormat="1" ht="20" thickBot="1">
       <c r="A1" s="18" t="s">
         <v>666</v>
       </c>
@@ -25769,7 +25769,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -25801,7 +25801,7 @@
       </c>
       <c r="L2" s="17"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -25830,7 +25830,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -25862,7 +25862,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -25891,7 +25891,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -25920,7 +25920,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -25932,7 +25932,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" t="b">
         <v>1</v>
       </c>
@@ -25961,7 +25961,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" t="b">
         <v>1</v>
       </c>
@@ -25990,7 +25990,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" t="b">
         <v>0</v>
       </c>
@@ -26020,7 +26020,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -26033,7 +26033,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" s="17" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" s="17" customFormat="1" ht="17" customHeight="1">
       <c r="A12" s="17" t="b">
         <v>1</v>
       </c>
@@ -26065,7 +26065,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="A13" t="b">
         <v>1</v>
       </c>
@@ -26094,7 +26094,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="A14" t="b">
         <v>1</v>
       </c>
@@ -26123,7 +26123,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="A15" t="b">
         <v>1</v>
       </c>
@@ -26152,7 +26152,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="A16" t="b">
         <v>1</v>
       </c>
@@ -26181,7 +26181,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" t="b">
         <v>1</v>
       </c>
@@ -26210,7 +26210,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" t="b">
         <v>1</v>
       </c>
@@ -26239,7 +26239,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" t="b">
         <v>1</v>
       </c>
@@ -26268,7 +26268,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" t="b">
         <v>1</v>
       </c>
@@ -26297,7 +26297,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" t="b">
         <v>1</v>
       </c>
@@ -26326,7 +26326,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" t="b">
         <v>1</v>
       </c>
@@ -26355,7 +26355,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" t="b">
         <v>1</v>
       </c>
@@ -26384,7 +26384,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="A24" t="b">
         <v>1</v>
       </c>
@@ -26413,7 +26413,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" t="b">
         <v>1</v>
       </c>
@@ -26442,7 +26442,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="A26" t="b">
         <v>1</v>
       </c>
@@ -26471,7 +26471,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" s="17" customFormat="1">
       <c r="A27" s="17" t="b">
         <v>0</v>
       </c>
@@ -26503,7 +26503,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -26515,7 +26515,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="A29" t="b">
         <v>0</v>
       </c>
@@ -26544,7 +26544,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="A30" t="b">
         <v>0</v>
       </c>
@@ -26573,7 +26573,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12">
       <c r="A31" t="b">
         <v>1</v>
       </c>
@@ -26600,7 +26600,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="A32" t="b">
         <v>1</v>
       </c>
@@ -26627,7 +26627,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="16" customHeight="1">
       <c r="A33" t="b">
         <v>1</v>
       </c>
@@ -26652,7 +26652,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="20" customHeight="1">
       <c r="A34" t="b">
         <v>1</v>
       </c>
@@ -26677,7 +26677,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" t="b">
         <v>1</v>
       </c>
@@ -26706,7 +26706,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -26718,7 +26718,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" t="b">
         <v>1</v>
       </c>
@@ -26747,7 +26747,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" t="b">
         <v>1</v>
       </c>
@@ -26776,7 +26776,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" t="b">
         <v>1</v>
       </c>
@@ -26805,7 +26805,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" t="b">
         <v>1</v>
       </c>
@@ -26834,7 +26834,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" t="b">
         <v>1</v>
       </c>
@@ -26863,7 +26863,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" t="b">
         <v>1</v>
       </c>
@@ -26892,7 +26892,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" t="b">
         <v>1</v>
       </c>
@@ -26921,7 +26921,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" t="b">
         <v>1</v>
       </c>
@@ -26950,7 +26950,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -26962,7 +26962,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="17" customHeight="1">
       <c r="A46" t="b">
         <v>0</v>
       </c>
@@ -26991,7 +26991,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="16" customHeight="1">
       <c r="A47" t="b">
         <v>0</v>
       </c>
@@ -27020,7 +27020,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" t="b">
         <v>0</v>
       </c>
@@ -27049,7 +27049,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -27061,7 +27061,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12">
       <c r="A50" t="b">
         <v>1</v>
       </c>
@@ -27090,7 +27090,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12">
       <c r="A51" t="b">
         <v>1</v>
       </c>
@@ -27119,7 +27119,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -27131,7 +27131,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12">
       <c r="A53" t="b">
         <v>0</v>
       </c>
@@ -27165,7 +27165,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12">
       <c r="A54" t="b">
         <v>0</v>
       </c>
@@ -27196,7 +27196,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12">
       <c r="A55" t="b">
         <v>0</v>
       </c>
@@ -27227,7 +27227,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -27239,7 +27239,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12">
       <c r="A57" t="b">
         <v>1</v>
       </c>
@@ -27266,7 +27266,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12">
       <c r="A58" t="b">
         <v>0</v>
       </c>
@@ -27297,7 +27297,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12">
       <c r="A59" t="b">
         <v>0</v>
       </c>
@@ -27328,7 +27328,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -27340,7 +27340,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="1"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12">
       <c r="A61" t="b">
         <v>0</v>
       </c>
@@ -27371,7 +27371,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12">
       <c r="A62" t="b">
         <v>0</v>
       </c>
@@ -27402,7 +27402,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12">
       <c r="A63" t="b">
         <v>0</v>
       </c>
@@ -27433,7 +27433,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -27445,7 +27445,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12">
       <c r="A65" t="b">
         <v>1</v>
       </c>
@@ -27474,7 +27474,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -27486,7 +27486,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12">
       <c r="A67" t="b">
         <v>0</v>
       </c>
@@ -27517,7 +27517,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12">
       <c r="A68" t="b">
         <v>0</v>
       </c>
@@ -27546,7 +27546,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12">
       <c r="A69" t="b">
         <v>0</v>
       </c>
@@ -27575,7 +27575,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -27587,7 +27587,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12">
       <c r="A71" t="b">
         <v>0</v>
       </c>
@@ -27618,7 +27618,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12">
       <c r="A72" t="b">
         <v>0</v>
       </c>
@@ -27647,7 +27647,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -27659,7 +27659,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="19" customHeight="1">
       <c r="A74" t="b">
         <v>1</v>
       </c>
@@ -27689,7 +27689,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12">
       <c r="A75" t="b">
         <v>0</v>
       </c>
@@ -27720,7 +27720,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12">
       <c r="A76" t="b">
         <v>0</v>
       </c>
@@ -27751,7 +27751,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -27763,7 +27763,7 @@
       <c r="J77" s="6"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12">
       <c r="A78" t="b">
         <v>0</v>
       </c>
@@ -27794,7 +27794,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12">
       <c r="A79" t="b">
         <v>0</v>
       </c>
@@ -27825,7 +27825,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12">
       <c r="A80" t="b">
         <v>0</v>
       </c>
@@ -27856,7 +27856,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -27868,7 +27868,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12">
       <c r="A82" t="b">
         <v>0</v>
       </c>
@@ -27899,7 +27899,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12">
       <c r="A83" t="b">
         <v>0</v>
       </c>
@@ -27930,7 +27930,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12">
       <c r="A84" t="b">
         <v>0</v>
       </c>
@@ -27961,7 +27961,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -27973,7 +27973,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12">
       <c r="A86" t="b">
         <v>1</v>
       </c>
@@ -28000,7 +28000,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12">
       <c r="A87" t="b">
         <v>1</v>
       </c>

--- a/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FBB2A9-AF9D-0442-A2AB-565E65037983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7715B2-6530-D44C-B85D-24D37FC76ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20860" activeTab="6" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20860" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2769" uniqueCount="811">
   <si>
     <t>Reporter</t>
   </si>
@@ -2529,6 +2529,12 @@
   </si>
   <si>
     <t>sample_collect_date + '/!/' + sample_collect_time + '/!/' + time_zone</t>
+  </si>
+  <si>
+    <t>vs_institution_type</t>
+  </si>
+  <si>
+    <t>{{institution_type}}</t>
   </si>
 </sst>
 </file>
@@ -2710,7 +2716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2787,9 +2793,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -13959,7 +13962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3154BFCE-06D9-9649-B340-B23DCF20DD83}">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -15352,7 +15355,7 @@
     </row>
     <row r="79" spans="1:8" s="23" customFormat="1">
       <c r="A79" s="23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B79" s="23" t="s">
         <v>630</v>
@@ -15392,7 +15395,7 @@
       </c>
       <c r="H80" s="39"/>
     </row>
-    <row r="81" spans="1:10" s="23" customFormat="1">
+    <row r="81" spans="1:8" s="23" customFormat="1">
       <c r="A81" s="23" t="b">
         <v>1</v>
       </c>
@@ -15413,7 +15416,7 @@
       </c>
       <c r="H81" s="39"/>
     </row>
-    <row r="82" spans="1:10" s="23" customFormat="1">
+    <row r="82" spans="1:8" s="23" customFormat="1">
       <c r="A82" s="23" t="b">
         <v>1</v>
       </c>
@@ -15434,7 +15437,7 @@
       </c>
       <c r="H82" s="39"/>
     </row>
-    <row r="83" spans="1:10" s="23" customFormat="1" ht="17" customHeight="1">
+    <row r="83" spans="1:8" s="23" customFormat="1" ht="17" customHeight="1">
       <c r="A83" s="23" t="b">
         <v>1</v>
       </c>
@@ -15455,7 +15458,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="84" spans="1:10" s="23" customFormat="1">
+    <row r="84" spans="1:8" s="23" customFormat="1">
       <c r="A84" s="23" t="b">
         <v>1</v>
       </c>
@@ -15477,7 +15480,7 @@
       </c>
       <c r="H84" s="39"/>
     </row>
-    <row r="85" spans="1:10" s="23" customFormat="1">
+    <row r="85" spans="1:8" s="23" customFormat="1">
       <c r="A85" s="23" t="b">
         <v>1</v>
       </c>
@@ -15498,7 +15501,7 @@
       </c>
       <c r="H85" s="39"/>
     </row>
-    <row r="86" spans="1:10" s="23" customFormat="1">
+    <row r="86" spans="1:8" s="23" customFormat="1">
       <c r="A86" s="23" t="b">
         <v>1</v>
       </c>
@@ -15519,393 +15522,25 @@
       </c>
       <c r="H86" s="39"/>
     </row>
-    <row r="87" spans="1:10" s="17" customFormat="1" ht="17" customHeight="1">
-      <c r="A87" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B87" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C87" s="23" t="s">
+    <row r="87" spans="1:8">
+      <c r="A87" t="b">
+        <v>1</v>
+      </c>
+      <c r="B87" t="s">
+        <v>630</v>
+      </c>
+      <c r="C87" t="s">
         <v>15</v>
       </c>
-      <c r="D87" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="E87" s="23" t="s">
+      <c r="E87" t="s">
         <v>76</v>
       </c>
-      <c r="F87" s="23" t="s">
+      <c r="F87" t="s">
         <v>100</v>
       </c>
-      <c r="G87" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H87" s="39"/>
-      <c r="I87" s="23"/>
-      <c r="J87" s="23"/>
-    </row>
-    <row r="88" spans="1:10" s="23" customFormat="1">
-      <c r="A88" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B88" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C88" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D88" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="E88" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F88" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G88" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="H88" s="39"/>
-    </row>
-    <row r="89" spans="1:10" s="23" customFormat="1">
-      <c r="A89" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B89" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C89" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D89" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="E89" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F89" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G89" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="H89" s="39"/>
-    </row>
-    <row r="90" spans="1:10" s="23" customFormat="1">
-      <c r="A90" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B90" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C90" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E90" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F90" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G90" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="H90" s="39"/>
-    </row>
-    <row r="91" spans="1:10" s="23" customFormat="1">
-      <c r="A91" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B91" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C91" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="E91" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F91" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G91" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="H91" s="39"/>
-    </row>
-    <row r="92" spans="1:10" s="23" customFormat="1">
-      <c r="A92" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B92" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C92" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D92" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="E92" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F92" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G92" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="H92" s="39"/>
-    </row>
-    <row r="93" spans="1:10" s="23" customFormat="1">
-      <c r="A93" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B93" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C93" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E93" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F93" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G93" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="H93" s="39"/>
-    </row>
-    <row r="94" spans="1:10" s="23" customFormat="1">
-      <c r="A94" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B94" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C94" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D94" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="E94" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F94" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G94" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="H94" s="39"/>
-    </row>
-    <row r="95" spans="1:10" s="23" customFormat="1">
-      <c r="A95" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B95" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C95" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E95" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F95" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G95" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="H95" s="39"/>
-    </row>
-    <row r="96" spans="1:10" s="23" customFormat="1">
-      <c r="A96" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B96" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C96" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D96" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E96" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F96" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G96" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="H96" s="39"/>
-    </row>
-    <row r="97" spans="1:11" s="23" customFormat="1">
-      <c r="A97" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B97" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C97" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D97" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="E97" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F97" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G97" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="H97" s="39"/>
-    </row>
-    <row r="98" spans="1:11" s="23" customFormat="1">
-      <c r="A98" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B98" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C98" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D98" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="E98" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F98" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G98" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H98" s="39"/>
-    </row>
-    <row r="99" spans="1:11" s="23" customFormat="1">
-      <c r="A99" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B99" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C99" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D99" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E99" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F99" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G99" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="H99" s="39"/>
-    </row>
-    <row r="100" spans="1:11" s="23" customFormat="1">
-      <c r="A100" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B100" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C100" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D100" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="E100" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F100" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G100" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="H100" s="39"/>
-    </row>
-    <row r="101" spans="1:11" s="23" customFormat="1">
-      <c r="A101" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B101" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C101" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D101" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E101" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F101" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G101" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="H101" s="39"/>
-    </row>
-    <row r="102" spans="1:11" s="23" customFormat="1">
-      <c r="A102" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B102" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C102" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D102" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E102" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F102" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G102" s="37" t="s">
-        <v>530</v>
-      </c>
-      <c r="H102" s="42"/>
-      <c r="I102" s="25"/>
-      <c r="K102" s="37"/>
+      <c r="G87" t="s">
+        <v>810</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20744,7 +20379,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC10C3F-0C27-5546-8767-E60C7CACEA9D}">
-  <dimension ref="A1:J191"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -23386,6 +23021,230 @@
       </c>
       <c r="I191" t="s">
         <v>532</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" t="b">
+        <v>1</v>
+      </c>
+      <c r="D193" t="s">
+        <v>809</v>
+      </c>
+      <c r="E193" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="I193" s="23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" t="b">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>809</v>
+      </c>
+      <c r="E194" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="I194" s="23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" t="b">
+        <v>1</v>
+      </c>
+      <c r="D195" t="s">
+        <v>809</v>
+      </c>
+      <c r="E195" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="I195" s="23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" t="b">
+        <v>1</v>
+      </c>
+      <c r="D196" t="s">
+        <v>809</v>
+      </c>
+      <c r="E196" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="I196" s="23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" t="b">
+        <v>1</v>
+      </c>
+      <c r="D197" t="s">
+        <v>809</v>
+      </c>
+      <c r="E197" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I197" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" t="b">
+        <v>1</v>
+      </c>
+      <c r="D198" t="s">
+        <v>809</v>
+      </c>
+      <c r="E198" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="I198" s="23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" t="b">
+        <v>1</v>
+      </c>
+      <c r="D199" t="s">
+        <v>809</v>
+      </c>
+      <c r="E199" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="I199" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" t="b">
+        <v>1</v>
+      </c>
+      <c r="D200" t="s">
+        <v>809</v>
+      </c>
+      <c r="E200" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="I200" s="23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" t="b">
+        <v>1</v>
+      </c>
+      <c r="D201" t="s">
+        <v>809</v>
+      </c>
+      <c r="E201" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="I201" s="23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" t="b">
+        <v>1</v>
+      </c>
+      <c r="D202" t="s">
+        <v>809</v>
+      </c>
+      <c r="E202" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="I202" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" t="b">
+        <v>1</v>
+      </c>
+      <c r="D203" t="s">
+        <v>809</v>
+      </c>
+      <c r="E203" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="I203" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" t="b">
+        <v>1</v>
+      </c>
+      <c r="D204" t="s">
+        <v>809</v>
+      </c>
+      <c r="E204" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="I204" s="23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" t="b">
+        <v>1</v>
+      </c>
+      <c r="D205" t="s">
+        <v>809</v>
+      </c>
+      <c r="E205" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="I205" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" t="b">
+        <v>1</v>
+      </c>
+      <c r="D206" t="s">
+        <v>809</v>
+      </c>
+      <c r="E206" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="I206" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" t="b">
+        <v>1</v>
+      </c>
+      <c r="D207" t="s">
+        <v>809</v>
+      </c>
+      <c r="E207" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="I207" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" t="b">
+        <v>1</v>
+      </c>
+      <c r="D208" t="s">
+        <v>809</v>
+      </c>
+      <c r="E208" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="I208" s="37" t="s">
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F7EBD55-827F-6243-BD48-0D9FEE1B89C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18857A13-B1CB-E84E-BE47-72AF98C007BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20860" activeTab="1" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">enums!$A$1:$J$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maps!$A$1:$K$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'maps original'!$A$1:$L$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide_measures!$A$1:$S$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">wide_measures!$A$1:$T$25</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
   </definedNames>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="820">
   <si>
     <t>Reporter</t>
   </si>
@@ -2281,9 +2281,6 @@
   </si>
   <si>
     <t>&lt;ignore&gt;</t>
-  </si>
-  <si>
-    <t>stepID_value</t>
   </si>
   <si>
     <t>value_expr</t>
@@ -2547,6 +2544,24 @@
   </si>
   <si>
     <t>extractRecov</t>
+  </si>
+  <si>
+    <t>summ_value</t>
+  </si>
+  <si>
+    <t>odm&gt;=3</t>
+  </si>
+  <si>
+    <t>odm&lt;3</t>
+  </si>
+  <si>
+    <t>percRec</t>
+  </si>
+  <si>
+    <t>selectors</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
@@ -14148,7 +14163,7 @@
         <v>713</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -14162,7 +14177,7 @@
         <v>713</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -14176,7 +14191,7 @@
         <v>713</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -14190,7 +14205,7 @@
         <v>713</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -14204,7 +14219,7 @@
         <v>713</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -14218,7 +14233,7 @@
         <v>713</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -14449,10 +14464,10 @@
         <v>114</v>
       </c>
       <c r="F28" s="25" t="s">
+        <v>752</v>
+      </c>
+      <c r="H28" s="34" t="s">
         <v>753</v>
-      </c>
-      <c r="H28" s="34" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -14569,7 +14584,7 @@
         <v>708</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -14604,7 +14619,7 @@
         <v>708</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -14618,7 +14633,7 @@
         <v>708</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -14632,7 +14647,7 @@
         <v>708</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -14646,7 +14661,7 @@
         <v>708</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -14799,7 +14814,7 @@
         <v>472</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G51" s="25" t="s">
         <v>689</v>
@@ -14919,7 +14934,7 @@
         <v>119</v>
       </c>
       <c r="H59" s="36" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -14937,10 +14952,10 @@
         <v>137</v>
       </c>
       <c r="H60" s="36" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
@@ -14960,7 +14975,7 @@
         <v>144</v>
       </c>
       <c r="H61" s="33" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -15390,7 +15405,7 @@
         <v>83</v>
       </c>
       <c r="H83" s="36" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -15471,7 +15486,7 @@
         <v>100</v>
       </c>
       <c r="G87" s="25" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -15482,30 +15497,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="25"/>
     <col min="2" max="2" width="13" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.83203125" style="25" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="83.6640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="21.83203125" style="25" customWidth="1"/>
-    <col min="19" max="19" width="27.6640625" style="25" customWidth="1"/>
-    <col min="20" max="16384" width="10.83203125" style="25"/>
+    <col min="3" max="3" width="13" style="25" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" style="25" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="83.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="21.83203125" style="25" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" style="25" customWidth="1"/>
+    <col min="21" max="16384" width="10.83203125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
         <v>651</v>
       </c>
@@ -15513,863 +15529,904 @@
         <v>614</v>
       </c>
       <c r="C1" s="31" t="s">
+        <v>818</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>616</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="E1" s="31" t="s">
         <v>617</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="F1" s="31" t="s">
         <v>618</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="G1" s="31" t="s">
         <v>620</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="H1" s="31" t="s">
         <v>667</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="I1" s="31" t="s">
         <v>732</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="J1" s="31" t="s">
+        <v>750</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>724</v>
+      </c>
+      <c r="L1" s="32" t="s">
+        <v>725</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>727</v>
+      </c>
+      <c r="N1" s="32" t="s">
+        <v>734</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>728</v>
+      </c>
+      <c r="P1" s="32" t="s">
+        <v>729</v>
+      </c>
+      <c r="Q1" s="31" t="s">
         <v>751</v>
       </c>
-      <c r="J1" s="32" t="s">
-        <v>724</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>725</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>727</v>
-      </c>
-      <c r="M1" s="32" t="s">
+      <c r="R1" s="31" t="s">
+        <v>744</v>
+      </c>
+      <c r="S1" s="31" t="s">
         <v>735</v>
       </c>
-      <c r="N1" s="32" t="s">
-        <v>728</v>
-      </c>
-      <c r="O1" s="32" t="s">
-        <v>729</v>
-      </c>
-      <c r="P1" s="31" t="s">
-        <v>752</v>
-      </c>
-      <c r="Q1" s="31" t="s">
-        <v>745</v>
-      </c>
-      <c r="R1" s="31" t="s">
-        <v>736</v>
-      </c>
-      <c r="S1" s="32" t="s">
+      <c r="T1" s="32" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="D2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="F2" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J2" s="25" t="s">
-        <v>799</v>
+      <c r="G2" s="25" t="s">
+        <v>630</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="M2" s="25" t="s">
-        <v>771</v>
-      </c>
       <c r="N2" s="25" t="s">
+        <v>770</v>
+      </c>
+      <c r="O2" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="P2" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B3" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="D3" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="F3" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F3" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J3" s="25" t="s">
+      <c r="G3" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K3" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="L3" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="M3" s="25" t="s">
         <v>633</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="O3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="P3" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="D4" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="F4" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J4" s="25" t="s">
+      <c r="G4" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K4" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="L4" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="M4" s="25" t="s">
         <v>632</v>
       </c>
-      <c r="N4" s="25" t="s">
+      <c r="O4" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="P4" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="D5" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="F5" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F5" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J5" s="25" t="s">
+      <c r="G5" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K5" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="K5" s="25" t="s">
+      <c r="L5" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="M5" s="25" t="s">
         <v>645</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="O5" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O5" s="25" t="s">
+      <c r="P5" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="D6" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="F6" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J6" s="25" t="s">
+      <c r="G6" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K6" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="K6" s="25" t="s">
+      <c r="L6" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="M6" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="N6" s="25" t="s">
+      <c r="O6" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="O6" s="25" t="s">
+      <c r="P6" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="D7" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="F7" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J7" s="25" t="s">
+      <c r="G7" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K7" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="L7" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="M7" s="25" t="s">
         <v>646</v>
       </c>
-      <c r="N7" s="25" t="s">
-        <v>756</v>
-      </c>
       <c r="O7" s="25" t="s">
+        <v>755</v>
+      </c>
+      <c r="P7" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="D8" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="F8" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F8" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>799</v>
+      <c r="G8" s="25" t="s">
+        <v>630</v>
       </c>
       <c r="K8" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="L8" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="M8" s="25" t="s">
-        <v>770</v>
-      </c>
       <c r="N8" s="25" t="s">
+        <v>769</v>
+      </c>
+      <c r="O8" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="O8" s="25" t="s">
+      <c r="P8" s="25" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="D9" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="F9" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F9" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J9" s="25" t="s">
+      <c r="G9" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K9" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="K9" s="25" t="s">
+      <c r="L9" s="25" t="s">
         <v>624</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="M9" s="25" t="s">
         <v>649</v>
       </c>
-      <c r="N9" s="25" t="s">
+      <c r="O9" s="25" t="s">
         <v>628</v>
       </c>
-      <c r="O9" s="25" t="s">
+      <c r="P9" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="P9" s="25" t="s">
+      <c r="Q9" s="25" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>623</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>648</v>
+      </c>
+      <c r="O10" s="25" t="s">
+        <v>627</v>
+      </c>
+      <c r="P10" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q10" s="25" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="25" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>623</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>648</v>
-      </c>
-      <c r="N10" s="25" t="s">
-        <v>627</v>
-      </c>
-      <c r="O10" s="25" t="s">
+      <c r="G11" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="L11" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="N11" s="25" t="s">
+        <v>768</v>
+      </c>
+      <c r="O11" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="P11" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="P10" s="25" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="25" t="s">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F11" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J11" s="25" t="s">
-        <v>799</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="M11" s="25" t="s">
-        <v>769</v>
-      </c>
-      <c r="N11" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="O11" s="25" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="25" t="str">
+      <c r="G12" s="25" t="str">
         <f>"true"</f>
         <v>true</v>
       </c>
-      <c r="J12" s="25" t="s">
-        <v>799</v>
-      </c>
       <c r="K12" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="L12" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="M12" s="25" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="D13" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="E13" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="F13" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F13" s="25" t="str">
+      <c r="G13" s="25" t="str">
         <f>"false"</f>
         <v>false</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="b">
         <v>1</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="D14" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="E14" s="25" t="s">
         <v>720</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="F14" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="G14" s="25" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L15" s="25" t="s">
+        <v>582</v>
+      </c>
+      <c r="M15" s="25" t="s">
+        <v>647</v>
+      </c>
+      <c r="O15" s="25" t="s">
+        <v>626</v>
+      </c>
+      <c r="P15" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q15" s="25" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>738</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>625</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>650</v>
+      </c>
+      <c r="O16" s="25" t="s">
+        <v>629</v>
+      </c>
+      <c r="P16" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q16" s="25" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="N17" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="O17" s="25" t="s">
+        <v>626</v>
+      </c>
+      <c r="P17" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q17" s="25" t="s">
+        <v>743</v>
+      </c>
+      <c r="R17" s="25" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L18" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="N18" s="25" t="s">
+        <v>788</v>
+      </c>
+      <c r="O18" s="25" t="s">
+        <v>626</v>
+      </c>
+      <c r="P18" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="Q18" s="25" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L19" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="N19" s="25" t="s">
+        <v>787</v>
+      </c>
+      <c r="O19" s="25" t="s">
+        <v>626</v>
+      </c>
+      <c r="P19" s="25" t="s">
+        <v>578</v>
+      </c>
+      <c r="Q19" s="25" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L20" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="N20" s="25" t="s">
+        <v>786</v>
+      </c>
+      <c r="O20" s="25" t="s">
+        <v>626</v>
+      </c>
+      <c r="P20" s="25" t="s">
+        <v>812</v>
+      </c>
+      <c r="Q20" s="25" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L21" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21" s="25" t="s">
+        <v>642</v>
+      </c>
+      <c r="O21" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="P21" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="M22" s="25" t="s">
+        <v>621</v>
+      </c>
+      <c r="S22" s="25" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L23" s="25" t="s">
+        <v>566</v>
+      </c>
+      <c r="M23" s="25" t="s">
+        <v>640</v>
+      </c>
+      <c r="O23" s="25" t="s">
+        <v>567</v>
+      </c>
+      <c r="P23" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="L24" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="25" t="s">
+      <c r="O24" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="P24" s="26" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F15" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J15" s="25" t="s">
+      <c r="G25" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K25" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="K15" s="25" t="s">
-        <v>582</v>
-      </c>
-      <c r="L15" s="25" t="s">
-        <v>647</v>
-      </c>
-      <c r="N15" s="25" t="s">
-        <v>626</v>
-      </c>
-      <c r="O15" s="25" t="s">
+      <c r="L25" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="25" t="s">
+        <v>644</v>
+      </c>
+      <c r="O25" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="P25" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>816</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="L27" s="25" t="s">
+        <v>817</v>
+      </c>
+      <c r="N27" s="25" t="s">
+        <v>784</v>
+      </c>
+      <c r="O27" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="P27" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="P15" s="25" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="25" t="s">
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A28" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>815</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>739</v>
-      </c>
-      <c r="J16" s="25" t="s">
+      <c r="G28" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="K28" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="K16" s="25" t="s">
-        <v>625</v>
-      </c>
-      <c r="L16" s="25" t="s">
-        <v>650</v>
-      </c>
-      <c r="N16" s="25" t="s">
-        <v>629</v>
-      </c>
-      <c r="O16" s="25" t="s">
+      <c r="L28" s="25" t="s">
+        <v>813</v>
+      </c>
+      <c r="N28" s="25" t="s">
+        <v>784</v>
+      </c>
+      <c r="O28" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="P28" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="P16" s="25" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>622</v>
-      </c>
-      <c r="M17" s="25" t="s">
-        <v>786</v>
-      </c>
-      <c r="N17" s="25" t="s">
-        <v>626</v>
-      </c>
-      <c r="O17" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="P17" s="25" t="s">
-        <v>744</v>
-      </c>
-      <c r="Q17" s="25" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>622</v>
-      </c>
-      <c r="M18" s="25" t="s">
-        <v>789</v>
-      </c>
-      <c r="N18" s="25" t="s">
-        <v>626</v>
-      </c>
-      <c r="O18" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="P18" s="25" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J19" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K19" s="25" t="s">
-        <v>622</v>
-      </c>
-      <c r="M19" s="25" t="s">
-        <v>788</v>
-      </c>
-      <c r="N19" s="25" t="s">
-        <v>626</v>
-      </c>
-      <c r="O19" s="25" t="s">
-        <v>578</v>
-      </c>
-      <c r="P19" s="25" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K20" s="25" t="s">
-        <v>622</v>
-      </c>
-      <c r="M20" s="25" t="s">
-        <v>787</v>
-      </c>
-      <c r="N20" s="25" t="s">
-        <v>626</v>
-      </c>
-      <c r="O20" s="25" t="s">
-        <v>813</v>
-      </c>
-      <c r="P20" s="25" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K21" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="L21" s="25" t="s">
-        <v>642</v>
-      </c>
-      <c r="N21" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="O21" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="L22" s="25" t="s">
-        <v>621</v>
-      </c>
-      <c r="R22" s="25" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K23" s="25" t="s">
-        <v>814</v>
-      </c>
-      <c r="M23" s="25" t="s">
-        <v>785</v>
-      </c>
-      <c r="N23" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="O23" s="25" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J24" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K24" s="25" t="s">
-        <v>566</v>
-      </c>
-      <c r="L24" s="25" t="s">
-        <v>640</v>
-      </c>
-      <c r="N24" s="25" t="s">
-        <v>567</v>
-      </c>
-      <c r="O24" s="25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J25" s="25" t="s">
-        <v>799</v>
-      </c>
-      <c r="K25" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26" t="s">
-        <v>768</v>
-      </c>
-      <c r="N25" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="O25" s="26" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="J26" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K26" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="L26" s="25" t="s">
-        <v>644</v>
-      </c>
-      <c r="N26" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="O26" s="25" t="s">
-        <v>153</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S28">
-    <sortCondition ref="C1:C28"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T29">
+    <sortCondition ref="D1:D29"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -16430,7 +16487,7 @@
         <v>721</v>
       </c>
       <c r="L1" s="32" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="M1" s="32" t="s">
         <v>120</v>
@@ -16450,10 +16507,10 @@
         <v>146</v>
       </c>
       <c r="K2" s="40" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="L2" s="40" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16710,14 +16767,13 @@
     <col min="5" max="5" width="12.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" style="25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" style="25" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" style="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5" style="25" customWidth="1"/>
+    <col min="8" max="8" width="21.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="18.5" style="25" customWidth="1"/>
     <col min="16" max="16" width="96.33203125" style="25" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="10.83203125" style="25"/>
   </cols>
@@ -16745,28 +16801,28 @@
         <v>667</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>798</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>734</v>
+        <v>797</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>725</v>
       </c>
       <c r="J1" s="32" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K1" s="32" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L1" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M1" s="32" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>729</v>
+        <v>814</v>
       </c>
       <c r="O1" s="32" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P1" s="32" t="s">
         <v>120</v>
@@ -16791,14 +16847,13 @@
       <c r="H2" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J2" s="25" t="s">
-        <v>630</v>
+        <v>479</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>479</v>
-      </c>
-      <c r="L2" s="25" t="s">
         <v>639</v>
       </c>
     </row>
@@ -16818,17 +16873,16 @@
       <c r="H3" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="26"/>
-      <c r="J3" s="25" t="s">
+      <c r="I3" s="25" t="s">
         <v>568</v>
       </c>
+      <c r="K3" s="25" t="s">
+        <v>662</v>
+      </c>
       <c r="L3" s="25" t="s">
-        <v>662</v>
+        <v>169</v>
       </c>
       <c r="M3" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="N3" s="25" t="s">
         <v>156</v>
       </c>
     </row>
@@ -16851,14 +16905,13 @@
       <c r="H4" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J4" s="25" t="s">
-        <v>630</v>
+        <v>499</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>499</v>
-      </c>
-      <c r="L4" s="25" t="s">
         <v>641</v>
       </c>
     </row>
@@ -16881,20 +16934,19 @@
       <c r="H5" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25" t="s">
+        <v>475</v>
+      </c>
       <c r="J5" s="25" t="s">
-        <v>475</v>
+        <v>630</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="L5" s="25" t="s">
-        <v>635</v>
+        <v>166</v>
       </c>
       <c r="M5" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="N5" s="25" t="s">
         <v>153</v>
       </c>
     </row>
@@ -16917,20 +16969,19 @@
       <c r="H6" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25" t="s">
+        <v>474</v>
+      </c>
       <c r="J6" s="25" t="s">
-        <v>474</v>
+        <v>630</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>634</v>
+        <v>155</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="N6" s="25" t="s">
         <v>153</v>
       </c>
     </row>
@@ -16953,20 +17004,19 @@
       <c r="H7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="26"/>
+      <c r="I7" s="25" t="s">
+        <v>477</v>
+      </c>
       <c r="J7" s="25" t="s">
-        <v>477</v>
+        <v>630</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>637</v>
+        <v>166</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="N7" s="25" t="s">
         <v>153</v>
       </c>
     </row>
@@ -16989,20 +17039,19 @@
       <c r="H8" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="26"/>
+      <c r="I8" s="25" t="s">
+        <v>476</v>
+      </c>
       <c r="J8" s="25" t="s">
-        <v>476</v>
+        <v>630</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>636</v>
+        <v>155</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="N8" s="25" t="s">
         <v>153</v>
       </c>
     </row>
@@ -17025,22 +17074,18 @@
       <c r="H9" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="26"/>
-      <c r="J9" s="25" t="s">
+      <c r="I9" s="25" t="s">
         <v>478</v>
       </c>
+      <c r="K9" s="25" t="s">
+        <v>638</v>
+      </c>
       <c r="L9" s="25" t="s">
-        <v>638</v>
+        <v>799</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>800</v>
-      </c>
-      <c r="N9" s="25" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="b">
@@ -17050,20 +17095,22 @@
         <v>615</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>151</v>
       </c>
       <c r="H11" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>811</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>819</v>
+      </c>
+      <c r="N11" s="25" t="s">
         <v>782</v>
-      </c>
-      <c r="I11" s="26"/>
-      <c r="K11" s="25" t="s">
-        <v>812</v>
-      </c>
-      <c r="L11" s="25" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -17088,13 +17135,13 @@
       <c r="H13" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I13" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J13" s="25" t="s">
-        <v>630</v>
+        <v>423</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>423</v>
-      </c>
-      <c r="L13" s="25" t="s">
         <v>656</v>
       </c>
     </row>
@@ -17120,13 +17167,13 @@
       <c r="H14" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I14" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J14" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K14" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L14" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -17152,13 +17199,13 @@
       <c r="H15" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I15" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J15" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L15" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -17184,17 +17231,17 @@
       <c r="H16" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I16" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J16" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K16" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L16" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="25" t="b">
         <v>1</v>
       </c>
@@ -17216,14 +17263,14 @@
       <c r="H17" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I17" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J17" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="K17" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="25" t="b">
         <v>1</v>
       </c>
@@ -17245,17 +17292,17 @@
       <c r="H18" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I18" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J18" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K18" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L18" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="b">
         <v>1</v>
       </c>
@@ -17277,17 +17324,17 @@
       <c r="H19" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I19" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J19" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K19" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L19" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="b">
         <v>1</v>
       </c>
@@ -17309,17 +17356,17 @@
       <c r="H20" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I20" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J20" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K20" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L20" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="b">
         <v>1</v>
       </c>
@@ -17341,17 +17388,17 @@
       <c r="H21" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I21" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J21" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K21" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L21" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="b">
         <v>1</v>
       </c>
@@ -17373,17 +17420,17 @@
       <c r="H22" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I22" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J22" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K22" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L22" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="25" t="b">
         <v>1</v>
       </c>
@@ -17405,17 +17452,17 @@
       <c r="H23" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I23" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J23" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K23" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L23" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="25" t="b">
         <v>1</v>
       </c>
@@ -17437,17 +17484,17 @@
       <c r="H24" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I24" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J24" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K24" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L24" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="b">
         <v>1</v>
       </c>
@@ -17469,17 +17516,17 @@
       <c r="H25" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I25" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J25" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K25" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L25" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="b">
         <v>1</v>
       </c>
@@ -17501,17 +17548,17 @@
       <c r="H26" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I26" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J26" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K26" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L26" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="25" t="b">
         <v>1</v>
       </c>
@@ -17533,17 +17580,17 @@
       <c r="H27" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I27" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J27" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K27" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L27" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="25" t="b">
         <v>1</v>
       </c>
@@ -17565,17 +17612,17 @@
       <c r="H28" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I28" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J28" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K28" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L28" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="25" t="b">
         <v>1</v>
       </c>
@@ -17597,17 +17644,17 @@
       <c r="H29" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I29" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J29" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K29" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L29" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="b">
         <v>1</v>
       </c>
@@ -17629,17 +17676,17 @@
       <c r="H30" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I30" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J30" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K30" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L30" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="25" t="b">
         <v>1</v>
       </c>
@@ -17661,17 +17708,17 @@
       <c r="H31" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I31" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J31" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K31" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L31" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="25" t="b">
         <v>1</v>
       </c>
@@ -17693,17 +17740,17 @@
       <c r="H32" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I32" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J32" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K32" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L32" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="25" t="b">
         <v>1</v>
       </c>
@@ -17725,17 +17772,17 @@
       <c r="H33" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I33" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J33" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K33" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L33" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="25" t="b">
         <v>1</v>
       </c>
@@ -17757,17 +17804,17 @@
       <c r="H34" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I34" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J34" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K34" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L34" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="25" t="b">
         <v>1</v>
       </c>
@@ -17789,17 +17836,17 @@
       <c r="H35" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I35" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J35" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K35" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L35" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="b">
         <v>1</v>
       </c>
@@ -17821,20 +17868,20 @@
       <c r="H36" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="I36" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J36" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K36" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L36" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D37" s="28"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="b">
         <v>1</v>
       </c>
@@ -17856,18 +17903,17 @@
       <c r="H38" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="I38" s="26"/>
+      <c r="I38" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J38" s="25" t="s">
-        <v>630</v>
+        <v>442</v>
       </c>
       <c r="K38" s="25" t="s">
-        <v>442</v>
-      </c>
-      <c r="L38" s="25" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="25" t="b">
         <v>1</v>
       </c>
@@ -17889,17 +17935,17 @@
       <c r="H39" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I39" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J39" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K39" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L39" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="25" t="b">
         <v>1</v>
       </c>
@@ -17921,17 +17967,17 @@
       <c r="H40" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I40" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J40" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K40" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L40" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="25" t="b">
         <v>1</v>
       </c>
@@ -17953,17 +17999,17 @@
       <c r="H41" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I41" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J41" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K41" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L41" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="25" t="b">
         <v>1</v>
       </c>
@@ -17985,17 +18031,17 @@
       <c r="H42" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I42" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J42" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K42" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L42" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="25" t="b">
         <v>1</v>
       </c>
@@ -18017,17 +18063,17 @@
       <c r="H43" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I43" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J43" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K43" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L43" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="25" t="b">
         <v>1</v>
       </c>
@@ -18049,17 +18095,17 @@
       <c r="H44" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I44" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J44" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K44" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L44" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="25" t="b">
         <v>1</v>
       </c>
@@ -18081,17 +18127,17 @@
       <c r="H45" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I45" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J45" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K45" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L45" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="25" t="b">
         <v>1</v>
       </c>
@@ -18113,17 +18159,17 @@
       <c r="H46" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I46" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J46" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K46" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L46" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="25" t="b">
         <v>1</v>
       </c>
@@ -18145,17 +18191,17 @@
       <c r="H47" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I47" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J47" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K47" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L47" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="25" t="b">
         <v>1</v>
       </c>
@@ -18177,17 +18223,17 @@
       <c r="H48" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I48" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J48" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K48" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L48" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="25" t="b">
         <v>1</v>
       </c>
@@ -18209,17 +18255,17 @@
       <c r="H49" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I49" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J49" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K49" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L49" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="25" t="b">
         <v>1</v>
       </c>
@@ -18241,17 +18287,17 @@
       <c r="H50" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I50" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J50" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K50" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L50" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="25" t="b">
         <v>1</v>
       </c>
@@ -18273,17 +18319,17 @@
       <c r="H51" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I51" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J51" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K51" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L51" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="25" t="b">
         <v>1</v>
       </c>
@@ -18305,17 +18351,17 @@
       <c r="H52" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I52" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J52" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K52" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L52" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="25" t="b">
         <v>1</v>
       </c>
@@ -18337,17 +18383,17 @@
       <c r="H53" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I53" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J53" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K53" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L53" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="25" t="b">
         <v>1</v>
       </c>
@@ -18369,17 +18415,17 @@
       <c r="H54" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I54" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J54" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K54" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L54" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="25" t="b">
         <v>1</v>
       </c>
@@ -18401,17 +18447,17 @@
       <c r="H55" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I55" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J55" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K55" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L55" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="25" t="b">
         <v>1</v>
       </c>
@@ -18433,17 +18479,17 @@
       <c r="H56" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I56" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J56" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K56" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L56" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="25" t="b">
         <v>1</v>
       </c>
@@ -18465,17 +18511,17 @@
       <c r="H57" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I57" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J57" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K57" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L57" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="25" t="b">
         <v>1</v>
       </c>
@@ -18497,17 +18543,17 @@
       <c r="H58" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I58" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J58" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K58" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L58" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="25" t="b">
         <v>1</v>
       </c>
@@ -18529,17 +18575,17 @@
       <c r="H59" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I59" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J59" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K59" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L59" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="25" t="b">
         <v>1</v>
       </c>
@@ -18561,17 +18607,17 @@
       <c r="H60" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I60" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J60" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K60" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L60" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="25" t="b">
         <v>1</v>
       </c>
@@ -18593,17 +18639,17 @@
       <c r="H61" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I61" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J61" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K61" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L61" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="25" t="b">
         <v>1</v>
       </c>
@@ -18625,17 +18671,17 @@
       <c r="H62" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I62" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J62" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K62" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L62" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="25" t="b">
         <v>1</v>
       </c>
@@ -18657,17 +18703,17 @@
       <c r="H63" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I63" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J63" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K63" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L63" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="25" t="b">
         <v>1</v>
       </c>
@@ -18689,13 +18735,13 @@
       <c r="H64" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I64" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J64" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K64" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L64" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18721,13 +18767,13 @@
       <c r="H65" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I65" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J65" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K65" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L65" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18753,13 +18799,13 @@
       <c r="H66" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I66" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J66" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K66" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L66" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18785,13 +18831,13 @@
       <c r="H67" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I67" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J67" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K67" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L67" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18817,13 +18863,13 @@
       <c r="H68" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I68" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J68" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K68" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L68" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18849,13 +18895,13 @@
       <c r="H69" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I69" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J69" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L69" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18881,13 +18927,13 @@
       <c r="H70" s="25" t="s">
         <v>30</v>
       </c>
+      <c r="I70" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J70" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L70" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18916,14 +18962,13 @@
       <c r="H72" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="I72" s="26"/>
+      <c r="I72" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J72" s="25" t="s">
-        <v>630</v>
+        <v>464</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>464</v>
-      </c>
-      <c r="L72" s="25" t="s">
         <v>660</v>
       </c>
     </row>
@@ -18949,13 +18994,13 @@
       <c r="H73" s="25" t="s">
         <v>41</v>
       </c>
+      <c r="I73" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J73" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K73" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L73" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -18981,13 +19026,13 @@
       <c r="H74" s="25" t="s">
         <v>41</v>
       </c>
+      <c r="I74" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J74" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L74" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -19013,13 +19058,13 @@
       <c r="H75" s="25" t="s">
         <v>41</v>
       </c>
+      <c r="I75" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J75" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K75" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L75" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -19045,13 +19090,13 @@
       <c r="H76" s="25" t="s">
         <v>41</v>
       </c>
+      <c r="I76" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J76" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K76" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L76" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -19077,13 +19122,13 @@
       <c r="H77" s="25" t="s">
         <v>41</v>
       </c>
+      <c r="I77" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J77" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K77" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L77" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -19109,13 +19154,13 @@
       <c r="H78" s="25" t="s">
         <v>41</v>
       </c>
+      <c r="I78" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J78" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K78" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L78" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -19144,21 +19189,20 @@
       <c r="H80" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="I80" s="26"/>
+      <c r="I80" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J80" s="25" t="s">
-        <v>630</v>
+        <v>502</v>
       </c>
       <c r="K80" s="25" t="s">
-        <v>502</v>
-      </c>
-      <c r="L80" s="25" t="s">
         <v>661</v>
       </c>
       <c r="O80" s="25" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="25" t="b">
         <v>1</v>
       </c>
@@ -19180,22 +19224,20 @@
       <c r="H81" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="I81" s="26"/>
+      <c r="I81" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J81" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K81" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L81" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D82" s="28"/>
-      <c r="I82" s="26"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="25" t="b">
         <v>1</v>
       </c>
@@ -19214,18 +19256,17 @@
       <c r="H83" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="I83" s="26"/>
+      <c r="I83" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J83" s="25" t="s">
-        <v>630</v>
+        <v>481</v>
       </c>
       <c r="K83" s="25" t="s">
-        <v>481</v>
-      </c>
-      <c r="L83" s="25" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="25" t="b">
         <v>1</v>
       </c>
@@ -19247,17 +19288,17 @@
       <c r="H84" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="I84" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J84" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K84" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L84" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="25" t="b">
         <v>1</v>
       </c>
@@ -19279,17 +19320,17 @@
       <c r="H85" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="I85" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J85" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K85" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L85" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="25" t="b">
         <v>1</v>
       </c>
@@ -19311,17 +19352,17 @@
       <c r="H86" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="I86" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J86" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K86" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L86" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="25" t="b">
         <v>1</v>
       </c>
@@ -19343,17 +19384,17 @@
       <c r="H87" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="I87" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J87" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K87" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L87" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="25" t="b">
         <v>1</v>
       </c>
@@ -19375,17 +19416,17 @@
       <c r="H88" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="I88" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J88" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K88" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L88" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="25" t="b">
         <v>1</v>
       </c>
@@ -19407,20 +19448,20 @@
       <c r="H89" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="I89" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J89" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K89" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L89" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D90" s="28"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="25" t="b">
         <v>1</v>
       </c>
@@ -19439,18 +19480,17 @@
       <c r="H91" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="I91" s="26"/>
+      <c r="I91" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J91" s="25" t="s">
-        <v>630</v>
+        <v>480</v>
       </c>
       <c r="K91" s="25" t="s">
-        <v>480</v>
-      </c>
-      <c r="L91" s="25" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="25" t="b">
         <v>1</v>
       </c>
@@ -19472,17 +19512,17 @@
       <c r="H92" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I92" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J92" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K92" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L92" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="b">
         <v>1</v>
       </c>
@@ -19504,17 +19544,17 @@
       <c r="H93" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I93" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J93" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K93" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L93" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="25" t="b">
         <v>1</v>
       </c>
@@ -19536,17 +19576,17 @@
       <c r="H94" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I94" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J94" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K94" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L94" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="25" t="b">
         <v>1</v>
       </c>
@@ -19568,17 +19608,17 @@
       <c r="H95" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I95" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J95" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K95" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L95" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="25" t="b">
         <v>1</v>
       </c>
@@ -19600,17 +19640,17 @@
       <c r="H96" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I96" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J96" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K96" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L96" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="b">
         <v>1</v>
       </c>
@@ -19632,17 +19672,17 @@
       <c r="H97" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I97" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J97" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K97" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L97" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="25" t="b">
         <v>1</v>
       </c>
@@ -19664,17 +19704,17 @@
       <c r="H98" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I98" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J98" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K98" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L98" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="25" t="b">
         <v>1</v>
       </c>
@@ -19696,17 +19736,17 @@
       <c r="H99" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I99" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J99" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K99" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L99" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="25" t="b">
         <v>1</v>
       </c>
@@ -19728,17 +19768,17 @@
       <c r="H100" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I100" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J100" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K100" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L100" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="25" t="b">
         <v>1</v>
       </c>
@@ -19760,17 +19800,17 @@
       <c r="H101" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I101" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J101" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K101" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L101" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="25" t="b">
         <v>1</v>
       </c>
@@ -19792,17 +19832,17 @@
       <c r="H102" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I102" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J102" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K102" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L102" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="25" t="b">
         <v>1</v>
       </c>
@@ -19824,17 +19864,17 @@
       <c r="H103" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I103" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J103" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K103" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L103" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="25" t="b">
         <v>1</v>
       </c>
@@ -19856,17 +19896,17 @@
       <c r="H104" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I104" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J104" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K104" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L104" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="25" t="b">
         <v>1</v>
       </c>
@@ -19888,17 +19928,17 @@
       <c r="H105" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I105" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J105" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K105" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L105" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="25" t="b">
         <v>1</v>
       </c>
@@ -19920,20 +19960,20 @@
       <c r="H106" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="I106" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J106" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K106" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L106" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D107" s="28"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="25" t="b">
         <v>1</v>
       </c>
@@ -19955,17 +19995,17 @@
       <c r="H108" s="25" t="s">
         <v>28</v>
       </c>
+      <c r="I108" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J108" s="25" t="s">
-        <v>630</v>
+        <v>418</v>
       </c>
       <c r="K108" s="25" t="s">
-        <v>418</v>
-      </c>
-      <c r="L108" s="25" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="25" t="b">
         <v>1</v>
       </c>
@@ -19987,17 +20027,17 @@
       <c r="H109" s="25" t="s">
         <v>28</v>
       </c>
+      <c r="I109" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J109" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K109" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L109" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="25" t="b">
         <v>1</v>
       </c>
@@ -20019,17 +20059,17 @@
       <c r="H110" s="25" t="s">
         <v>28</v>
       </c>
+      <c r="I110" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J110" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K110" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L110" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="25" t="b">
         <v>1</v>
       </c>
@@ -20051,17 +20091,17 @@
       <c r="H111" s="25" t="s">
         <v>28</v>
       </c>
+      <c r="I111" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J111" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K111" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="L111" s="25" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="25" t="b">
         <v>1</v>
       </c>
@@ -20080,13 +20120,13 @@
       <c r="H112" s="25" t="s">
         <v>28</v>
       </c>
+      <c r="I112" s="25" t="s">
+        <v>630</v>
+      </c>
       <c r="J112" s="25" t="s">
         <v>630</v>
       </c>
       <c r="K112" s="25" t="s">
-        <v>630</v>
-      </c>
-      <c r="L112" s="25" t="s">
         <v>630</v>
       </c>
     </row>
@@ -20143,37 +20183,37 @@
         <v>667</v>
       </c>
       <c r="H1" s="31" t="s">
+        <v>771</v>
+      </c>
+      <c r="I1" s="32" t="s">
         <v>772</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="J1" s="32" t="s">
         <v>773</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="K1" s="32" t="s">
         <v>774</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="L1" s="23" t="s">
+        <v>795</v>
+      </c>
+      <c r="M1" s="32" t="s">
         <v>775</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="N1" s="32" t="s">
+        <v>776</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>777</v>
+      </c>
+      <c r="P1" s="23" t="s">
         <v>796</v>
       </c>
-      <c r="M1" s="32" t="s">
-        <v>776</v>
-      </c>
-      <c r="N1" s="32" t="s">
-        <v>777</v>
-      </c>
-      <c r="O1" s="32" t="s">
-        <v>778</v>
-      </c>
-      <c r="P1" s="23" t="s">
-        <v>797</v>
-      </c>
       <c r="Q1" s="32" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="R1" s="31" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -20199,7 +20239,7 @@
         <v>40</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O2" s="25" t="s">
         <v>655</v>
@@ -20208,7 +20248,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -20234,7 +20274,7 @@
         <v>28</v>
       </c>
       <c r="M3" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O3" s="25" t="s">
         <v>634</v>
@@ -20243,7 +20283,7 @@
         <v>31</v>
       </c>
       <c r="Q3" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -20269,7 +20309,7 @@
         <v>32</v>
       </c>
       <c r="M4" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O4" s="25" t="s">
         <v>634</v>
@@ -20278,7 +20318,7 @@
         <v>31</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -20304,7 +20344,7 @@
         <v>31</v>
       </c>
       <c r="M5" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O5" s="25" t="s">
         <v>656</v>
@@ -20313,7 +20353,7 @@
         <v>29</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -20339,7 +20379,7 @@
         <v>35</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O6" s="25" t="s">
         <v>656</v>
@@ -20348,7 +20388,7 @@
         <v>29</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -20374,7 +20414,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O7" s="25" t="s">
         <v>636</v>
@@ -20383,7 +20423,7 @@
         <v>33</v>
       </c>
       <c r="Q7" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -20409,7 +20449,7 @@
         <v>34</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O8" s="25" t="s">
         <v>636</v>
@@ -20418,7 +20458,7 @@
         <v>33</v>
       </c>
       <c r="Q8" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -20444,7 +20484,7 @@
         <v>33</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O9" s="25" t="s">
         <v>657</v>
@@ -20453,7 +20493,7 @@
         <v>30</v>
       </c>
       <c r="Q9" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -20479,7 +20519,7 @@
         <v>36</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O10" s="25" t="s">
         <v>657</v>
@@ -20488,7 +20528,7 @@
         <v>30</v>
       </c>
       <c r="Q10" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -20514,7 +20554,7 @@
         <v>37</v>
       </c>
       <c r="M11" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O11" s="25" t="s">
         <v>639</v>
@@ -20523,7 +20563,7 @@
         <v>36</v>
       </c>
       <c r="Q11" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -20549,7 +20589,7 @@
         <v>38</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O12" s="25" t="s">
         <v>639</v>
@@ -20558,7 +20598,7 @@
         <v>36</v>
       </c>
       <c r="Q12" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -20584,7 +20624,7 @@
         <v>30</v>
       </c>
       <c r="M13" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O13" s="25" t="s">
         <v>660</v>
@@ -20593,7 +20633,7 @@
         <v>41</v>
       </c>
       <c r="Q13" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
@@ -20619,7 +20659,7 @@
         <v>42</v>
       </c>
       <c r="M14" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O14" s="25" t="s">
         <v>660</v>
@@ -20628,7 +20668,7 @@
         <v>41</v>
       </c>
       <c r="Q14" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
@@ -20639,7 +20679,7 @@
         <v>615</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>710</v>
@@ -20648,13 +20688,13 @@
         <v>688</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L15" s="25" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="M15" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O15" s="25" t="s">
         <v>660</v>
@@ -20663,7 +20703,7 @@
         <v>41</v>
       </c>
       <c r="Q15" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -20689,7 +20729,7 @@
         <v>43</v>
       </c>
       <c r="M16" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O16" s="25" t="s">
         <v>660</v>
@@ -20698,7 +20738,7 @@
         <v>41</v>
       </c>
       <c r="Q16" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -20886,7 +20926,7 @@
         <v>395</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -21343,7 +21383,7 @@
         <v>395</v>
       </c>
       <c r="I46" s="25" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -21669,7 +21709,7 @@
         <v>289</v>
       </c>
       <c r="I70" s="25" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
@@ -22663,7 +22703,7 @@
         <v>360</v>
       </c>
       <c r="I141" s="25" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
@@ -22677,7 +22717,7 @@
         <v>361</v>
       </c>
       <c r="I142" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
@@ -22691,7 +22731,7 @@
         <v>362</v>
       </c>
       <c r="I143" s="25" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
@@ -22705,7 +22745,7 @@
         <v>363</v>
       </c>
       <c r="I144" s="25" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
@@ -22719,7 +22759,7 @@
         <v>364</v>
       </c>
       <c r="I145" s="25" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
@@ -22733,7 +22773,7 @@
         <v>365</v>
       </c>
       <c r="I146" s="25" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
@@ -22747,7 +22787,7 @@
         <v>366</v>
       </c>
       <c r="I147" s="25" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
@@ -23142,7 +23182,7 @@
         <v>258</v>
       </c>
       <c r="I176" s="25" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
@@ -23156,7 +23196,7 @@
         <v>259</v>
       </c>
       <c r="I177" s="25" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
@@ -23360,7 +23400,7 @@
         <v>1</v>
       </c>
       <c r="D193" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E193" s="27" t="s">
         <v>84</v>
@@ -23374,7 +23414,7 @@
         <v>1</v>
       </c>
       <c r="D194" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E194" s="27" t="s">
         <v>85</v>
@@ -23388,7 +23428,7 @@
         <v>1</v>
       </c>
       <c r="D195" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E195" s="41" t="s">
         <v>86</v>
@@ -23402,7 +23442,7 @@
         <v>1</v>
       </c>
       <c r="D196" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E196" s="41" t="s">
         <v>87</v>
@@ -23416,7 +23456,7 @@
         <v>1</v>
       </c>
       <c r="D197" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E197" s="41" t="s">
         <v>88</v>
@@ -23430,7 +23470,7 @@
         <v>1</v>
       </c>
       <c r="D198" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E198" s="28" t="s">
         <v>89</v>
@@ -23444,7 +23484,7 @@
         <v>1</v>
       </c>
       <c r="D199" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E199" s="28" t="s">
         <v>90</v>
@@ -23458,7 +23498,7 @@
         <v>1</v>
       </c>
       <c r="D200" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E200" s="27" t="s">
         <v>91</v>
@@ -23472,7 +23512,7 @@
         <v>1</v>
       </c>
       <c r="D201" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E201" s="27" t="s">
         <v>92</v>
@@ -23486,7 +23526,7 @@
         <v>1</v>
       </c>
       <c r="D202" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E202" s="28" t="s">
         <v>93</v>
@@ -23500,7 +23540,7 @@
         <v>1</v>
       </c>
       <c r="D203" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E203" s="28" t="s">
         <v>94</v>
@@ -23514,7 +23554,7 @@
         <v>1</v>
       </c>
       <c r="D204" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E204" s="28" t="s">
         <v>95</v>
@@ -23528,7 +23568,7 @@
         <v>1</v>
       </c>
       <c r="D205" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E205" s="28" t="s">
         <v>96</v>
@@ -23542,7 +23582,7 @@
         <v>1</v>
       </c>
       <c r="D206" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E206" s="28" t="s">
         <v>97</v>
@@ -23556,7 +23596,7 @@
         <v>1</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E207" s="28" t="s">
         <v>98</v>
@@ -23570,7 +23610,7 @@
         <v>1</v>
       </c>
       <c r="D208" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E208" s="28" t="s">
         <v>99</v>

--- a/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18857A13-B1CB-E84E-BE47-72AF98C007BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8BA9DB-380B-524D-A3A5-A3B4A0585CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20860" activeTab="1" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20860" activeTab="3" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="820">
   <si>
     <t>Reporter</t>
   </si>
@@ -2561,7 +2561,7 @@
     <t>selectors</t>
   </si>
   <si>
-    <t>null</t>
+    <t>case(((inhibition_method == "") + (inhibition_method == None), ""), (True, "null"))</t>
   </si>
 </sst>
 </file>
@@ -16757,7 +16757,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC6A21B-0669-0743-9D12-F41DCA15CA4A}">
-  <dimension ref="A1:P112"/>
+  <dimension ref="A1:Q112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="25" bestFit="1" customWidth="1"/>
@@ -16771,14 +16771,15 @@
     <col min="9" max="9" width="15.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5" style="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="18.5" style="25" customWidth="1"/>
-    <col min="16" max="16" width="96.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="10.83203125" style="25"/>
+    <col min="12" max="12" width="22.83203125" style="25" customWidth="1"/>
+    <col min="13" max="13" width="11" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="18.5" style="25" customWidth="1"/>
+    <col min="17" max="17" width="96.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="10.83203125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="31" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="31" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>651</v>
       </c>
@@ -16813,22 +16814,25 @@
         <v>727</v>
       </c>
       <c r="L1" s="32" t="s">
+        <v>734</v>
+      </c>
+      <c r="M1" s="32" t="s">
         <v>728</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="N1" s="32" t="s">
         <v>729</v>
       </c>
-      <c r="N1" s="32" t="s">
+      <c r="O1" s="32" t="s">
         <v>814</v>
       </c>
-      <c r="O1" s="32" t="s">
+      <c r="P1" s="32" t="s">
         <v>751</v>
       </c>
-      <c r="P1" s="32" t="s">
+      <c r="Q1" s="32" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="b">
         <v>1</v>
       </c>
@@ -16857,7 +16861,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="b">
         <v>1</v>
       </c>
@@ -16879,14 +16883,14 @@
       <c r="K3" s="25" t="s">
         <v>662</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="M3" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="N3" s="25" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="b">
         <v>1</v>
       </c>
@@ -16915,7 +16919,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="b">
         <v>1</v>
       </c>
@@ -16943,14 +16947,14 @@
       <c r="K5" s="25" t="s">
         <v>635</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="M5" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="N5" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="b">
         <v>1</v>
       </c>
@@ -16978,14 +16982,14 @@
       <c r="K6" s="25" t="s">
         <v>634</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="M6" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="N6" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="b">
         <v>1</v>
       </c>
@@ -17013,14 +17017,14 @@
       <c r="K7" s="25" t="s">
         <v>637</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="M7" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="N7" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="b">
         <v>1</v>
       </c>
@@ -17048,14 +17052,14 @@
       <c r="K8" s="25" t="s">
         <v>636</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="M8" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="M8" s="25" t="s">
+      <c r="N8" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="b">
         <v>1</v>
       </c>
@@ -17080,14 +17084,14 @@
       <c r="K9" s="25" t="s">
         <v>638</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="M9" s="25" t="s">
         <v>799</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="N9" s="25" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="b">
         <v>1</v>
       </c>
@@ -17106,14 +17110,14 @@
       <c r="J11" s="25" t="s">
         <v>811</v>
       </c>
-      <c r="K11" s="25" t="s">
+      <c r="L11" s="25" t="s">
         <v>819</v>
       </c>
-      <c r="N11" s="25" t="s">
+      <c r="O11" s="25" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="b">
         <v>1</v>
       </c>
@@ -17145,7 +17149,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="b">
         <v>1</v>
       </c>
@@ -17177,7 +17181,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="b">
         <v>1</v>
       </c>
@@ -17209,7 +17213,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="b">
         <v>1</v>
       </c>
@@ -18745,7 +18749,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="25" t="b">
         <v>1</v>
       </c>
@@ -18777,7 +18781,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" s="25" t="b">
         <v>1</v>
       </c>
@@ -18809,7 +18813,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" s="25" t="b">
         <v>1</v>
       </c>
@@ -18841,7 +18845,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" s="25" t="b">
         <v>1</v>
       </c>
@@ -18873,7 +18877,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" s="25" t="b">
         <v>1</v>
       </c>
@@ -18905,7 +18909,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" s="25" t="b">
         <v>1</v>
       </c>
@@ -18937,10 +18941,10 @@
         <v>630</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D71" s="30"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" s="25" t="b">
         <v>1</v>
       </c>
@@ -18972,7 +18976,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" s="25" t="b">
         <v>1</v>
       </c>
@@ -19004,7 +19008,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" s="25" t="b">
         <v>1</v>
       </c>
@@ -19036,7 +19040,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" s="25" t="b">
         <v>1</v>
       </c>
@@ -19068,7 +19072,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" s="25" t="b">
         <v>1</v>
       </c>
@@ -19100,7 +19104,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" s="25" t="b">
         <v>1</v>
       </c>
@@ -19132,7 +19136,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" s="25" t="b">
         <v>1</v>
       </c>
@@ -19164,10 +19168,10 @@
         <v>630</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D79" s="28"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" s="25" t="b">
         <v>1</v>
       </c>
@@ -19198,7 +19202,7 @@
       <c r="K80" s="25" t="s">
         <v>661</v>
       </c>
-      <c r="O80" s="25" t="s">
+      <c r="P80" s="25" t="s">
         <v>747</v>
       </c>
     </row>

--- a/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/nwss_to_odm_v2_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8BA9DB-380B-524D-A3A5-A3B4A0585CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB8F50E-EBDD-E543-853E-4B4BFB98E95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20860" activeTab="3" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="40960" windowHeight="20760" xr2:uid="{77810E24-F86B-BC44-A0D5-8790E6EC60B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="822">
   <si>
     <t>Reporter</t>
   </si>
@@ -2562,6 +2562,12 @@
   </si>
   <si>
     <t>case(((inhibition_method == "") + (inhibition_method == None), ""), (True, "null"))</t>
+  </si>
+  <si>
+    <t>pop</t>
+  </si>
+  <si>
+    <t>peeps</t>
   </si>
 </sst>
 </file>
@@ -2857,6 +2863,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="parts"/>
@@ -15309,7 +15316,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B79" s="25" t="s">
         <v>615</v>
@@ -15497,7 +15504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39AC7DD-3F73-2C47-925D-21E5B4EBE6FC}">
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="25"/>
@@ -16421,6 +16428,35 @@
         <v>161</v>
       </c>
       <c r="P28" s="25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A30" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>820</v>
+      </c>
+      <c r="L30" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="M30" s="25" t="s">
+        <v>681</v>
+      </c>
+      <c r="O30" s="25" t="s">
+        <v>821</v>
+      </c>
+      <c r="P30" s="25" t="s">
         <v>156</v>
       </c>
     </row>
@@ -23803,7 +23839,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>1</v>
